--- a/files/九龙-何文田-朗贤峰第IIB期.xlsx
+++ b/files/九龙-何文田-朗贤峰第IIB期.xlsx
@@ -8,10 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6A座 销控表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6B座 销控表" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -114,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -179,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -195,45 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -618,7 +482,7 @@
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>朗贤峯第IIB期 - 一手销控汇总明细</t>
+          <t>朗贤峰第IIB期 - 一手销控汇总明细</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1125,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -7797,7 +7661,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10373,7 +10237,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -10419,7 +10283,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -12066,7 +11930,7 @@
         </is>
       </c>
       <c r="E250" s="4" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
@@ -12082,7 +11946,7 @@
         <v>7362000</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>19023</v>
+        <v>18974</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
@@ -13685,7 +13549,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -13731,7 +13595,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -15483,7 +15347,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -20175,7 +20039,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -20313,7 +20177,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -20731,7 +20595,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -21743,7 +21607,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H460" s="5" t="n">
@@ -23721,7 +23585,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H503" s="5" t="n">
@@ -24319,7 +24183,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H516" s="5" t="n">
@@ -25423,7 +25287,7 @@
       </c>
       <c r="G540" s="3" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H540" s="5" t="n">
@@ -27009,5796 +26873,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>朗贤峯第IIB期 - 5A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>143 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>122 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>21 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1304呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 390呎 (1房)
-$880万
-$22,559/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,467万
-$27,219/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,333万
-$27,316/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 554呎 (2房)
-$1,915万
-$34,574/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$2,031万
-$25,935/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,336万
-$24,924/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$836万
-$21,549/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,338万
-$24,827/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,216万
-$24,922/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,447万
-$26,077/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$2,021万
-$25,808/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,621万
-$30,244/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$815万
-$20,995/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,325万
-$24,584/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,263万
-$25,883/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,748万
-$31,492/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$1,992万
-$25,434/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,310万
-$24,438/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$805万
-$20,747/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,300万
-$24,109/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,210万
-$24,791/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,440万
-$25,941/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$1,982万
-$25,310/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,590万
-$29,657/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$803万
-$20,706/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,287万
-$23,874/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,170万
-$23,965/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,426万
-$25,686/呎
-(24年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$1,972万
-$25,186/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,582万
-$29,511/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$802万
-$20,665/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,274万
-$23,640/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,158万
-$23,732/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,365万
-$24,589/呎
-(24年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$2,010万
-$25,676/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,574万
-$29,366/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$800万
-$20,624/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,262万
-$23,410/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,147万
-$23,500/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,371万
-$24,703/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$1,953万
-$24,941/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,316万
-$24,547/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$799万
-$20,582/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,280万
-$23,746/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,163万
-$23,838/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,344万
-$24,223/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$1,991万
-$25,425/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,278万
-$23,845/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$817万
-$21,046/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,237万
-$22,954/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,152万
-$23,609/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,318万
-$23,755/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$1,943万
-$24,820/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,278万
-$23,845/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$797万
-$20,544/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,237万
-$22,954/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,125万
-$23,045/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,306万
-$23,524/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$1,924万
-$24,579/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,266万
-$23,612/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$792万
-$20,399/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,255万
-$23,284/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,141万
-$23,375/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,238万
-$22,305/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$1,962万
-$25,055/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,536万
-$28,655/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$790万
-$20,361/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,219万
-$22,620/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,115万
-$22,848/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,244万
-$22,405/呎
-(24年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$1,906万
-$24,340/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,528万
-$28,513/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$808万
-$20,817/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,272万
-$23,607/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,103万
-$22,596/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,211万
-$21,825/呎
-(24年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$1,896万
-$24,221/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,521万
-$28,375/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$806万
-$20,773/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,207万
-$22,397/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,124万
-$23,035/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,205万
-$21,717/呎
-(24年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$1,869万
-$23,870/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,499万
-$27,961/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$778万
-$20,041/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,231万
-$22,831/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,119万
-$22,922/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,171万
-$21,095/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$1,887万
-$24,098/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,477万
-$27,552/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$787万
-$20,289/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,225万
-$22,720/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,087万
-$22,266/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,165万
-$20,993/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$1,860万
-$23,750/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,455万
-$27,153/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$759万
-$19,570/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,219万
-$22,609/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,108万
-$22,699/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,188万
-$21,400/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$1,798万
-$22,959/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,210万
-$22,584/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$752万
-$19,379/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,219万
-$22,609/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,108万
-$22,699/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,188万
-$21,400/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$1,806万
-$23,068/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,413万
-$26,368/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$757万
-$19,521/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,178万
-$21,855/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,097万
-$22,480/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,148万
-$20,686/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$1,797万
-$22,955/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,406万
-$26,237/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$756万
-$19,482/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,201万
-$22,278/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,066万
-$21,834/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,142万
-$20,584/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$1,789万
-$22,844/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,400万
-$26,110/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$754万
-$19,446/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,166万
-$21,640/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,060万
-$21,727/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,137万
-$20,483/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$2,119万
-$27,063/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,393万
-$25,983/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$735万
-$18,943/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,189万
-$22,059/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,055万
-$21,621/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,131万
-$20,384/呎
-(24年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 783呎 (3房)
-$2,109万
-$26,931/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 536呎 (2房)
-$1,386万
-$25,856/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$734万
-$18,905/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 539呎 (2房)
-$1,155万
-$21,429/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,050万
-$21,516/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F | 555呎 (2房)
-$1,126万
-$20,283/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 740呎 (3房)
-$1,934万
-$26,134/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 498呎 (2房)
-$1,219万
-$24,474/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 350呎 (1房)
-$991万
-$28,314/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 502呎 (2房)
-$1,231万
-$24,518/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 450呎 (2房)
-$1,120万
-$24,889/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>F | 517呎 (2房)
-$1,171万
-$22,646/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>朗贤峯第IIB期 - 5B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>143 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>141 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1278呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$856万
-$22,106/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$858万
-$22,772/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$836万
-$22,175/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,402万
-$26,709/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,970万
-$26,026/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,627万
-$31,234/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$799万
-$20,651/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$801万
-$21,249/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 378呎 (1房)
-$780万
-$20,638/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,244万
-$23,688/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$2,046万
-$27,032/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,354万
-$25,983/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$798万
-$20,610/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$800万
-$21,207/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$779万
-$20,653/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,268万
-$24,145/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,960万
-$25,896/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,296万
-$24,871/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$807万
-$20,863/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$790万
-$20,958/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$788万
-$20,907/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,219万
-$23,223/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,895万
-$25,033/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,283万
-$24,628/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$787万
-$20,326/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$770万
-$20,416/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$768万
-$20,369/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,213万
-$23,109/呎
-(24年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,922万
-$25,394/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,271万
-$24,388/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$804万
-$20,780/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$768万
-$20,377/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$766万
-$20,329/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,207万
-$22,992/呎
-(24年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,904万
-$25,148/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,258万
-$24,150/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$784万
-$20,245/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$785万
-$20,833/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$765万
-$20,289/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,206万
-$22,981/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,840万
-$24,312/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,276万
-$24,497/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$801万
-$20,700/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$803万
-$21,289/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$763万
-$20,247/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,172万
-$22,324/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,867万
-$24,663/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,234万
-$23,681/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$780万
-$20,165/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$764万
-$20,255/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$780万
-$20,700/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,195万
-$22,754/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,822万
-$24,074/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,234万
-$23,681/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$780万
-$20,165/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$782万
-$20,748/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$799万
-$21,191/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 524呎 (2房)
-$1,195万
-$22,798/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,762万
-$23,273/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,252万
-$24,021/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$794万
-$20,514/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$777万
-$20,607/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$757万
-$20,069/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,155万
-$21,994/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,753万
-$23,160/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,216万
-$23,334/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$774万
-$19,987/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$757万
-$20,077/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$755万
-$20,029/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,149万
-$21,884/呎
-(24年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,745万
-$23,048/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,210万
-$23,221/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$772万
-$19,946/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$774万
-$20,525/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$754万
-$19,989/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,143万
-$21,777/呎
-(24年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,736万
-$22,935/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,233万
-$23,668/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$789万
-$20,393/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$754万
-$19,997/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$752万
-$19,950/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,138万
-$21,669/呎
-(24年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,728万
-$22,823/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,227万
-$23,555/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$761万
-$19,672/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$763万
-$20,241/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$761万
-$20,194/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,121万
-$21,349/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,761万
-$23,266/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,221万
-$23,440/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$752万
-$19,442/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$736万
-$19,528/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$752万
-$19,955/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,104万
-$21,034/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,711万
-$22,601/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,186万
-$22,768/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$762万
-$19,680/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$728万
-$19,297/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$726万
-$19,252/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,088万
-$20,726/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,711万
-$22,601/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,186万
-$22,768/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$736万
-$19,023/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 378呎 (1房)
-$738万
-$19,521/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$754万
-$19,989/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 524呎 (2房)
-$1,104万
-$21,063/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,694万
-$22,383/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,175万
-$22,545/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$724万
-$18,705/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$726万
-$19,249/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$724万
-$19,202/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,056万
-$20,120/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,686万
-$22,273/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,169万
-$22,436/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$722万
-$18,669/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$724万
-$19,210/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$705万
-$18,708/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,051万
-$20,021/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,678万
-$22,165/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,192万
-$22,869/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$739万
-$19,088/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$706万
-$18,716/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$704万
-$18,671/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,071万
-$20,408/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,670万
-$22,058/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,186万
-$22,758/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$737万
-$19,049/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$704万
-$18,679/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$702万
-$18,634/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,041万
-$19,823/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,702万
-$22,485/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,152万
-$22,107/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 387呎 (1房)
-$718万
-$18,558/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$703万
-$18,642/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$718万
-$19,050/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,036万
-$19,726/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,769万
-$24,707/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 481呎 (2房)
-$1,196万
-$24,871/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 350呎 (1房)
-$753万
-$21,509/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$732万
-$21,532/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 340呎 (1房)
-$748万
-$22,003/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>F | 487呎 (2房)
-$1,140万
-$23,405/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>朗贤峯第IIB期 - 6A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>143 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>142 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1287呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>B | 761呎 (3房)
-$1,960万
-$25,761/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,289万
-$25,932/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$863万
-$22,250/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>E | 391呎 (1房)
-$858万
-$21,944/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$2,051万
-$26,497/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,859万
-$24,455/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,142万
-$22,978/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$789万
-$20,330/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$808万
-$20,812/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,334万
-$25,263/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$2,030万
-$26,234/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,849万
-$24,334/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,136万
-$22,865/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$787万
-$20,289/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$773万
-$19,925/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,321万
-$25,013/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,991万
-$25,720/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,779万
-$23,408/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,147万
-$23,082/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$797万
-$20,544/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$758万
-$19,526/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,264万
-$23,939/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,924万
-$24,859/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,813万
-$23,861/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,142万
-$22,970/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$796万
-$20,503/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$745万
-$19,201/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,252万
-$23,703/呎
-(24年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,961万
-$25,339/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,762万
-$23,178/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,136万
-$22,855/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$794万
-$20,461/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 389呎 (1房)
-$752万
-$19,332/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,276万
-$24,161/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,952万
-$25,213/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,796万
-$23,626/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,130万
-$22,744/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$792万
-$20,423/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$727万
-$18,727/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,239万
-$23,468/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,942万
-$25,087/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,787万
-$23,511/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,125万
-$22,632/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 392呎 (1房)
-$772万
-$19,694/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$725万
-$18,691/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,263万
-$23,919/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,849万
-$23,893/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,778万
-$23,393/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,119万
-$22,523/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$789万
-$20,343/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$724万
-$18,652/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,257万
-$23,801/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,813万
-$23,424/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,736万
-$22,837/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,093万
-$21,986/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$770万
-$19,858/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$724万
-$18,652/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,232万
-$23,333/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,760万
-$22,742/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,719万
-$22,613/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,082万
-$21,773/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$784万
-$20,204/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 389呎 (1房)
-$719万
-$18,476/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,168万
-$22,116/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,759万
-$22,729/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,752万
-$23,050/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,103万
-$22,195/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$782万
-$20,162/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$735万
-$18,938/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,167万
-$22,102/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,716万
-$22,174/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,702万
-$22,391/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,098万
-$22,085/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$781万
-$20,124/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$733万
-$18,897/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,139万
-$21,564/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,635万
-$21,119/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,735万
-$22,824/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,066万
-$21,455/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$779万
-$20,085/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$714万
-$18,412/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,111万
-$21,036/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,634万
-$21,106/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,685万
-$22,171/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,087万
-$21,869/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$778万
-$20,046/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$730万
-$18,825/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,058万
-$20,036/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,593万
-$20,579/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,677万
-$22,062/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,056万
-$21,243/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$758万
-$19,531/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$712万
-$18,338/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,061万
-$20,100/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,547万
-$19,988/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,709万
-$22,488/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,051万
-$21,141/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$756万
-$19,492/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$710万
-$18,302/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,031万
-$19,525/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,547万
-$19,988/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,668万
-$21,953/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,051万
-$21,141/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$756万
-$19,492/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$710万
-$18,302/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,056万
-$20,000/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,569万
-$20,273/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,692万
-$22,268/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,066万
-$21,447/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$769万
-$19,830/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$705万
-$18,175/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,046万
-$19,803/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,561万
-$20,173/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,684万
-$22,159/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,042万
-$20,960/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$750万
-$19,322/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$704万
-$18,139/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,040万
-$19,706/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,517万
-$19,594/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,636万
-$21,525/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,030万
-$20,730/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$748万
-$19,284/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$720万
-$18,544/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,011万
-$19,140/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,509万
-$19,497/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,628万
-$21,418/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,025万
-$20,630/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$747万
-$19,245/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$718万
-$18,508/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,030万
-$19,509/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1,502万
-$19,401/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1,630万
-$21,443/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1,045万
-$21,030/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$764万
-$19,678/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$700万
-$18,031/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1,025万
-$19,413/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 732呎 (3房)
-$1,570万
-$21,455/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,742万
-$24,224/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 459呎 (2房)
-$1,062万
-$23,126/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 350呎 (1房)
-$793万
-$22,651/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 350呎 (1房)
-$756万
-$21,589/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-$1,068万
-$21,788/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>朗贤峯第IIB期 - 6B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>143 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>142 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1277呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$812万
-$20,938/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$810万
-$21,475/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$794万
-$21,064/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,259万
-$23,983/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,818万
-$24,011/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,267万
-$24,363/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$776万
-$20,005/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$737万
-$19,557/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$759万
-$20,130/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,143万
-$21,771/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,844万
-$24,354/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,254万
-$24,123/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$765万
-$19,716/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$736万
-$19,517/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$757万
-$20,090/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,165万
-$22,192/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,807万
-$23,876/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,230万
-$23,648/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$736万
-$18,961/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$727万
-$19,286/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$748万
-$19,851/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,120万
-$21,343/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,747万
-$23,077/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,218万
-$23,415/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$725万
-$18,680/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$726万
-$19,249/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$729万
-$19,342/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,142万
-$21,754/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,730万
-$22,848/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,177万
-$22,631/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$735万
-$18,938/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$742万
-$19,682/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$728万
-$19,302/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,136万
-$21,646/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,712万
-$22,622/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,194万
-$22,954/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$716万
-$18,451/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$723万
-$19,172/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$726万
-$19,265/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,082万
-$20,615/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,696万
-$22,398/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,182万
-$22,725/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$714万
-$18,415/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$739万
-$19,602/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$743万
-$19,698/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,077万
-$20,512/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,720万
-$22,716/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,142万
-$21,965/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$713万
-$18,376/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$720万
-$19,098/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$723万
-$19,188/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,072万
-$20,411/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,638万
-$21,635/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,170万
-$22,500/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$713万
-$18,376/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$720万
-$19,098/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$741万
-$19,655/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,098万
-$20,909/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,622万
-$21,421/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,131万
-$21,748/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$725万
-$18,693/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$732万
-$19,430/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 378呎 (1房)
-$736万
-$19,468/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,087万
-$20,703/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,614万
-$21,314/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,153万
-$22,165/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$724万
-$18,657/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$731万
-$19,390/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$717万
-$19,019/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,081万
-$20,598/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,645万
-$21,725/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,120万
-$21,533/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$705万
-$18,178/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$712万
-$18,891/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$716万
-$18,981/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,050万
-$20,008/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,636万
-$21,618/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,114万
-$21,425/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$721万
-$18,582/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$728万
-$19,310/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$732万
-$19,406/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,071万
-$20,394/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,628万
-$21,510/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,136万
-$21,837/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$702万
-$18,103/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$709万
-$18,814/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$713万
-$18,905/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 524呎 (2房)
-$1,040万
-$19,847/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,620万
-$21,403/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,130万
-$21,729/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$701万
-$18,067/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$708万
-$18,777/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$729万
-$19,326/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,060万
-$20,192/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,612万
-$21,297/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,124万
-$21,621/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$700万
-$18,031/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$724万
-$19,196/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$710万
-$18,830/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,055万
-$20,091/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,612万
-$21,297/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,098万
-$21,106/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$734万
-$18,912/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$741万
-$19,655/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$710万
-$18,830/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,030万
-$19,613/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,558万
-$20,584/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,087万
-$20,898/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$695万
-$17,907/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$719万
-$19,064/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$722万
-$19,156/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,020万
-$19,419/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,550万
-$20,481/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,108万
-$21,302/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$710万
-$18,307/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$717万
-$19,027/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$721万
-$19,117/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,039万
-$19,794/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,543万
-$20,379/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,102万
-$21,196/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$709万
-$18,271/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$699万
-$18,538/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$702万
-$18,626/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,009万
-$19,227/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,535万
-$20,277/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,097万
-$21,088/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$691万
-$17,799/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$698万
-$18,501/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$701万
-$18,589/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,004万
-$19,131/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1,565万
-$20,670/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,065万
-$20,485/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$706万
-$18,183/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$696万
-$18,464/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$699万
-$18,552/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1,024万
-$19,501/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,627万
-$22,722/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 480呎 (2房)
-$1,107万
-$23,058/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 350呎 (1房)
-$736万
-$21,029/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$742万
-$21,812/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 340呎 (1房)
-$746万
-$21,935/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>F | 487呎 (2房)
-$1,080万
-$22,181/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-何文田-朗贤峰第IIB期.xlsx
+++ b/files/九龙-何文田-朗贤峰第IIB期.xlsx
@@ -8,6 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5B座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6A座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6B座" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +45,91 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +140,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +221,57 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +648,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -26873,4 +27047,5796 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1304呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 390呎 (1房)
+$880万
+$22,559/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1467万
+$27,219/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1333万
+$27,316/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 554呎 (2房)
+$1915万
+$34,574/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$2031万
+$25,935/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1336万
+$24,924/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$836万
+$21,549/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1338万
+$24,827/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1216万
+$24,922/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1447万
+$26,077/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$2021万
+$25,808/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1621万
+$30,244/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$815万
+$20,995/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1325万
+$24,584/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1263万
+$25,883/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1748万
+$31,492/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$1992万
+$25,434/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1310万
+$24,438/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$805万
+$20,747/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1300万
+$24,109/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1210万
+$24,791/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1440万
+$25,941/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$1982万
+$25,310/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1590万
+$29,657/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$803万
+$20,706/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1287万
+$23,874/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1170万
+$23,965/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1426万
+$25,686/呎
+(24年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$1972万
+$25,186/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1582万
+$29,511/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$802万
+$20,665/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1274万
+$23,640/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1158万
+$23,732/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1365万
+$24,589/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$2010万
+$25,676/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1574万
+$29,366/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$800万
+$20,624/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1262万
+$23,410/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1147万
+$23,500/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1371万
+$24,703/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$1953万
+$24,941/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1316万
+$24,547/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$799万
+$20,582/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1280万
+$23,746/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1163万
+$23,838/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1344万
+$24,223/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$1991万
+$25,425/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1278万
+$23,845/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$817万
+$21,046/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1237万
+$22,954/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1152万
+$23,609/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1318万
+$23,755/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$1943万
+$24,820/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1278万
+$23,845/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$797万
+$20,544/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1237万
+$22,954/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1125万
+$23,045/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1306万
+$23,524/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$1924万
+$24,579/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1266万
+$23,612/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$792万
+$20,399/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1255万
+$23,284/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1141万
+$23,375/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1238万
+$22,305/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$1962万
+$25,055/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1536万
+$28,655/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$790万
+$20,361/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1219万
+$22,620/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1115万
+$22,848/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1244万
+$22,405/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$1906万
+$24,340/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1528万
+$28,513/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$808万
+$20,817/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1272万
+$23,607/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1103万
+$22,596/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1211万
+$21,825/呎
+(24年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$1896万
+$24,221/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1521万
+$28,375/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$806万
+$20,773/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1207万
+$22,397/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1124万
+$23,035/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1205万
+$21,717/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$1869万
+$23,870/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1499万
+$27,961/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$778万
+$20,041/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1231万
+$22,831/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1119万
+$22,922/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1171万
+$21,095/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$1887万
+$24,098/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1477万
+$27,552/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$787万
+$20,289/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1225万
+$22,720/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1087万
+$22,266/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1165万
+$20,993/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$1860万
+$23,750/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1455万
+$27,153/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$759万
+$19,570/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1219万
+$22,609/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1108万
+$22,699/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1188万
+$21,400/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$1798万
+$22,959/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1210万
+$22,584/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$752万
+$19,379/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1219万
+$22,609/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1108万
+$22,699/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1188万
+$21,400/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$1806万
+$23,068/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1413万
+$26,368/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$757万
+$19,521/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1178万
+$21,855/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1097万
+$22,480/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1148万
+$20,686/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$1797万
+$22,955/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1406万
+$26,237/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$756万
+$19,482/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1201万
+$22,278/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1066万
+$21,834/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1142万
+$20,584/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$1789万
+$22,844/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1400万
+$26,110/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$754万
+$19,446/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1166万
+$21,640/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1060万
+$21,727/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1137万
+$20,483/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$2119万
+$27,063/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1393万
+$25,983/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$735万
+$18,943/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1189万
+$22,059/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1055万
+$21,621/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1131万
+$20,384/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 783呎 (3房)
+$2109万
+$26,931/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 536呎 (2房)
+$1386万
+$25,856/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$734万
+$18,905/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 539呎 (2房)
+$1155万
+$21,429/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1050万
+$21,516/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 555呎 (2房)
+$1126万
+$20,283/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 740呎 (3房)
+$1934万
+$26,134/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 498呎 (2房)
+$1219万
+$24,474/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 350呎 (1房)
+$991万
+$28,314/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 502呎 (2房)
+$1231万
+$24,518/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 450呎 (2房)
+$1120万
+$24,889/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>F | 517呎 (2房)
+$1171万
+$22,646/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1278呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$856万
+$22,106/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$858万
+$22,772/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$836万
+$22,175/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1402万
+$26,709/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1970万
+$26,026/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1627万
+$31,234/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$799万
+$20,651/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$801万
+$21,249/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 378呎 (1房)
+$780万
+$20,638/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1244万
+$23,688/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$2046万
+$27,032/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1354万
+$25,983/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$798万
+$20,610/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$800万
+$21,207/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$779万
+$20,653/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1268万
+$24,145/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1960万
+$25,896/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1296万
+$24,871/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$807万
+$20,863/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$790万
+$20,958/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$788万
+$20,907/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1219万
+$23,223/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1895万
+$25,033/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1283万
+$24,628/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$787万
+$20,326/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$770万
+$20,416/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$768万
+$20,369/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1213万
+$23,109/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1922万
+$25,394/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1271万
+$24,388/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$804万
+$20,780/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$768万
+$20,377/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$766万
+$20,329/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1207万
+$22,992/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1904万
+$25,148/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1258万
+$24,150/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$784万
+$20,245/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$785万
+$20,833/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$765万
+$20,289/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1206万
+$22,981/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1840万
+$24,312/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1276万
+$24,497/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$801万
+$20,700/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$803万
+$21,289/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$763万
+$20,247/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1172万
+$22,324/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1867万
+$24,663/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1234万
+$23,681/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$780万
+$20,165/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$764万
+$20,255/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$780万
+$20,700/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1195万
+$22,754/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1822万
+$24,074/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1234万
+$23,681/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$780万
+$20,165/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$782万
+$20,748/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$799万
+$21,191/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 524呎 (2房)
+$1195万
+$22,798/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1762万
+$23,273/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1252万
+$24,021/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$794万
+$20,514/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$777万
+$20,607/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$757万
+$20,069/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1155万
+$21,994/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1753万
+$23,160/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1216万
+$23,334/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$774万
+$19,987/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$757万
+$20,077/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$755万
+$20,029/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1149万
+$21,884/呎
+(24年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1745万
+$23,048/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1210万
+$23,221/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$772万
+$19,946/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$774万
+$20,525/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$754万
+$19,989/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1143万
+$21,777/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1736万
+$22,935/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1233万
+$23,668/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$789万
+$20,393/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$754万
+$19,997/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$752万
+$19,950/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1138万
+$21,669/呎
+(24年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1728万
+$22,823/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1227万
+$23,555/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$761万
+$19,672/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$763万
+$20,241/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$761万
+$20,194/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1121万
+$21,349/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1761万
+$23,266/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1221万
+$23,440/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$752万
+$19,442/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$736万
+$19,528/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$752万
+$19,955/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1104万
+$21,034/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1711万
+$22,601/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1186万
+$22,768/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$762万
+$19,680/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$728万
+$19,297/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$726万
+$19,252/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1088万
+$20,726/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1711万
+$22,601/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1186万
+$22,768/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$736万
+$18,974/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 378呎 (1房)
+$738万
+$19,521/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$754万
+$19,989/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 524呎 (2房)
+$1104万
+$21,063/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1694万
+$22,383/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1175万
+$22,545/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$724万
+$18,705/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$726万
+$19,249/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$724万
+$19,202/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1056万
+$20,120/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1686万
+$22,273/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1169万
+$22,436/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$722万
+$18,669/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$724万
+$19,210/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$705万
+$18,708/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1051万
+$20,021/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1678万
+$22,165/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1192万
+$22,869/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$739万
+$19,088/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$706万
+$18,716/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$704万
+$18,671/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1071万
+$20,408/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1670万
+$22,058/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1186万
+$22,758/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$737万
+$19,049/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$704万
+$18,679/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$702万
+$18,634/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1041万
+$19,823/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1702万
+$22,485/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1152万
+$22,107/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 387呎 (1房)
+$718万
+$18,558/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$703万
+$18,642/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$718万
+$19,050/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1036万
+$19,726/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1769万
+$24,707/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 481呎 (2房)
+$1196万
+$24,871/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 350呎 (1房)
+$753万
+$21,509/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$732万
+$21,532/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 340呎 (1房)
+$748万
+$22,003/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>F | 487呎 (2房)
+$1140万
+$23,405/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>6A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1287呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 761呎 (3房)
+$1960万
+$25,761/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1289万
+$25,932/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$863万
+$22,250/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 391呎 (1房)
+$858万
+$21,944/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$2051万
+$26,497/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1859万
+$24,455/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1142万
+$22,978/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$789万
+$20,330/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$808万
+$20,812/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1334万
+$25,263/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$2030万
+$26,234/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1849万
+$24,334/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1136万
+$22,865/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$787万
+$20,289/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$773万
+$19,925/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1321万
+$25,013/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1991万
+$25,720/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1779万
+$23,408/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1147万
+$23,082/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$797万
+$20,544/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$758万
+$19,526/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1264万
+$23,939/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1924万
+$24,859/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1813万
+$23,861/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1142万
+$22,970/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$796万
+$20,503/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$745万
+$19,201/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1252万
+$23,703/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1961万
+$25,339/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1762万
+$23,178/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1136万
+$22,855/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$794万
+$20,461/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 389呎 (1房)
+$752万
+$19,332/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1276万
+$24,161/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1952万
+$25,213/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1796万
+$23,626/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1130万
+$22,744/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$792万
+$20,423/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$727万
+$18,727/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1239万
+$23,468/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1942万
+$25,087/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1787万
+$23,511/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1125万
+$22,632/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 392呎 (1房)
+$772万
+$19,694/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$725万
+$18,691/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1263万
+$23,919/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1849万
+$23,893/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1778万
+$23,393/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1119万
+$22,523/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$789万
+$20,343/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$724万
+$18,652/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1257万
+$23,801/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1813万
+$23,424/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1736万
+$22,837/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1093万
+$21,986/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$770万
+$19,858/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$724万
+$18,652/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1232万
+$23,333/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1760万
+$22,742/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1719万
+$22,613/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1082万
+$21,773/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$784万
+$20,204/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 389呎 (1房)
+$719万
+$18,476/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1168万
+$22,116/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1759万
+$22,729/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1752万
+$23,050/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1103万
+$22,195/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$782万
+$20,162/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$735万
+$18,938/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1167万
+$22,102/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1716万
+$22,174/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1702万
+$22,391/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1098万
+$22,085/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$781万
+$20,124/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$733万
+$18,897/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1139万
+$21,564/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1635万
+$21,119/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1735万
+$22,824/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1066万
+$21,455/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$779万
+$20,085/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$714万
+$18,412/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1111万
+$21,036/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1634万
+$21,106/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1685万
+$22,171/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1087万
+$21,869/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$778万
+$20,046/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$730万
+$18,825/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1058万
+$20,036/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1593万
+$20,579/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1677万
+$22,062/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1056万
+$21,243/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$758万
+$19,531/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$712万
+$18,338/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1061万
+$20,100/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1547万
+$19,988/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1709万
+$22,488/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1051万
+$21,141/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$756万
+$19,492/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$710万
+$18,302/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1031万
+$19,525/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1547万
+$19,988/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1668万
+$21,953/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1051万
+$21,141/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$756万
+$19,492/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$710万
+$18,302/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1056万
+$20,000/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1569万
+$20,273/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1692万
+$22,268/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1066万
+$21,447/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$769万
+$19,830/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$705万
+$18,175/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1046万
+$19,803/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1561万
+$20,173/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1684万
+$22,159/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1042万
+$20,960/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$750万
+$19,322/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$704万
+$18,139/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1040万
+$19,706/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1517万
+$19,594/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1636万
+$21,525/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1030万
+$20,730/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$748万
+$19,284/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$720万
+$18,544/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1011万
+$19,140/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1509万
+$19,497/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1628万
+$21,418/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1025万
+$20,630/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$747万
+$19,245/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$718万
+$18,508/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1030万
+$19,509/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1502万
+$19,401/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1630万
+$21,443/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1045万
+$21,030/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$764万
+$19,678/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$700万
+$18,031/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1025万
+$19,413/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 732呎 (3房)
+$1570万
+$21,455/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1742万
+$24,224/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 459呎 (2房)
+$1062万
+$23,126/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 350呎 (1房)
+$793万
+$22,651/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 350呎 (1房)
+$756万
+$21,589/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+$1068万
+$21,788/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>6B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1277呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$812万
+$20,938/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$810万
+$21,475/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$794万
+$21,064/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1259万
+$23,983/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1818万
+$24,011/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1267万
+$24,363/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$776万
+$20,005/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$737万
+$19,557/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$759万
+$20,130/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1143万
+$21,771/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1844万
+$24,354/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1254万
+$24,123/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$765万
+$19,716/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$736万
+$19,517/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$757万
+$20,090/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1165万
+$22,192/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1807万
+$23,876/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1230万
+$23,648/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$736万
+$18,961/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$727万
+$19,286/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$748万
+$19,851/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1120万
+$21,343/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1747万
+$23,077/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1218万
+$23,415/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$725万
+$18,680/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$726万
+$19,249/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$729万
+$19,342/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1142万
+$21,754/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1730万
+$22,848/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1177万
+$22,631/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$735万
+$18,938/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$742万
+$19,682/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$728万
+$19,302/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1136万
+$21,646/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1712万
+$22,622/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1194万
+$22,954/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$716万
+$18,451/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$723万
+$19,172/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$726万
+$19,265/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1082万
+$20,615/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1696万
+$22,398/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1182万
+$22,725/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$714万
+$18,415/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$739万
+$19,602/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$743万
+$19,698/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1077万
+$20,512/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1720万
+$22,716/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1142万
+$21,965/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$713万
+$18,376/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$720万
+$19,098/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$723万
+$19,188/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1072万
+$20,411/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1638万
+$21,635/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1170万
+$22,500/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$713万
+$18,376/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$720万
+$19,098/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$741万
+$19,655/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1098万
+$20,909/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1622万
+$21,421/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1131万
+$21,748/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$725万
+$18,693/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$732万
+$19,430/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 378呎 (1房)
+$736万
+$19,468/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1087万
+$20,703/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1614万
+$21,314/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1153万
+$22,165/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$724万
+$18,657/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$731万
+$19,390/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$717万
+$19,019/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1081万
+$20,598/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1645万
+$21,725/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1120万
+$21,533/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$705万
+$18,178/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$712万
+$18,891/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$716万
+$18,981/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1050万
+$20,008/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1636万
+$21,618/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1114万
+$21,425/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$721万
+$18,582/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$728万
+$19,310/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$732万
+$19,406/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1071万
+$20,394/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1628万
+$21,510/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1136万
+$21,837/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$702万
+$18,103/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$709万
+$18,814/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$713万
+$18,905/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 524呎 (2房)
+$1040万
+$19,847/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1620万
+$21,403/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1130万
+$21,729/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$701万
+$18,067/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$708万
+$18,777/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$729万
+$19,326/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1060万
+$20,192/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1612万
+$21,297/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1124万
+$21,621/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$700万
+$18,031/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$724万
+$19,196/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$710万
+$18,830/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1055万
+$20,091/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1612万
+$21,297/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1098万
+$21,106/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$734万
+$18,912/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$741万
+$19,655/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$710万
+$18,830/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1030万
+$19,613/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1558万
+$20,584/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1087万
+$20,898/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$695万
+$17,907/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$719万
+$19,064/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$722万
+$19,156/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1020万
+$19,419/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1550万
+$20,481/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1108万
+$21,302/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$710万
+$18,307/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$717万
+$19,027/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$721万
+$19,117/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1039万
+$19,794/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1543万
+$20,379/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1102万
+$21,196/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$709万
+$18,271/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$699万
+$18,538/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$702万
+$18,626/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1009万
+$19,227/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1535万
+$20,277/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1097万
+$21,088/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$691万
+$17,799/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$698万
+$18,501/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$701万
+$18,589/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1004万
+$19,131/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1565万
+$20,670/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1065万
+$20,485/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$706万
+$18,183/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$696万
+$18,464/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$699万
+$18,552/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1024万
+$19,501/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1627万
+$22,722/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 480呎 (2房)
+$1107万
+$23,058/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 350呎 (1房)
+$736万
+$21,029/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$742万
+$21,812/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 340呎 (1房)
+$746万
+$21,935/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>F | 487呎 (2房)
+$1080万
+$22,181/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-何文田-朗贤峰第IIB期.xlsx
+++ b/files/九龙-何文田-朗贤峰第IIB期.xlsx
@@ -648,7 +648,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-何文田-朗贤峰第IIB期.xlsx
+++ b/files/九龙-何文田-朗贤峰第IIB期.xlsx
@@ -12616,7 +12616,7 @@
         </is>
       </c>
       <c r="E194" s="4" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         <v>7804000</v>
       </c>
       <c r="I194" s="5" t="n">
-        <v>20700</v>
+        <v>20646</v>
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>7804000</v>
       </c>
       <c r="L194" s="5" t="n">
-        <v>20700</v>
+        <v>20646</v>
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
           <t>C | 390呎 (1房)
 $880万
 $22,559/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -36395,7 +36395,7 @@
           <t>D | 539呎 (2房)
 $1467万
 $27,219/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -36403,7 +36403,7 @@
           <t>E | 488呎 (2房)
 $1333万
 $27,316/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -36426,7 +36426,7 @@
           <t>A | 783呎 (3房)
 $2031万
 $25,935/呎
-(24年-10月-22日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -36434,7 +36434,7 @@
           <t>B | 536呎 (2房)
 $1336万
 $24,924/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -36442,7 +36442,7 @@
           <t>C | 388呎 (1房)
 $836万
 $21,549/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -36450,7 +36450,7 @@
           <t>D | 539呎 (2房)
 $1338万
 $24,827/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -36458,7 +36458,7 @@
           <t>E | 488呎 (2房)
 $1216万
 $24,922/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -36466,7 +36466,7 @@
           <t>F | 555呎 (2房)
 $1447万
 $26,077/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -36481,7 +36481,7 @@
           <t>A | 783呎 (3房)
 $2021万
 $25,808/呎
-(24年-10月-23日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -36497,7 +36497,7 @@
           <t>C | 388呎 (1房)
 $815万
 $20,995/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -36505,7 +36505,7 @@
           <t>D | 539呎 (2房)
 $1325万
 $24,584/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -36513,7 +36513,7 @@
           <t>E | 488呎 (2房)
 $1263万
 $25,883/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -36536,7 +36536,7 @@
           <t>A | 783呎 (3房)
 $1992万
 $25,434/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -36544,7 +36544,7 @@
           <t>B | 536呎 (2房)
 $1310万
 $24,438/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -36552,7 +36552,7 @@
           <t>C | 388呎 (1房)
 $805万
 $20,747/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -36560,7 +36560,7 @@
           <t>D | 539呎 (2房)
 $1300万
 $24,109/呎
-(24年-05月-30日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -36568,7 +36568,7 @@
           <t>E | 488呎 (2房)
 $1210万
 $24,791/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -36576,7 +36576,7 @@
           <t>F | 555呎 (2房)
 $1440万
 $25,941/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -36591,7 +36591,7 @@
           <t>A | 783呎 (3房)
 $1982万
 $25,310/呎
-(24年-10月-08日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -36607,7 +36607,7 @@
           <t>C | 388呎 (1房)
 $803万
 $20,706/呎
-(24年-07月-01日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -36615,7 +36615,7 @@
           <t>D | 539呎 (2房)
 $1287万
 $23,874/呎
-(24年-07月-24日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -36623,7 +36623,7 @@
           <t>E | 488呎 (2房)
 $1170万
 $23,965/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -36631,7 +36631,7 @@
           <t>F | 555呎 (2房)
 $1426万
 $25,686/呎
-(24年-07月-03日)</t>
+(24年-07月)</t>
         </is>
       </c>
     </row>
@@ -36646,7 +36646,7 @@
           <t>A | 783呎 (3房)
 $1972万
 $25,186/呎
-(24年-07月-16日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -36662,7 +36662,7 @@
           <t>C | 388呎 (1房)
 $802万
 $20,665/呎
-(24年-06月-27日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -36670,7 +36670,7 @@
           <t>D | 539呎 (2房)
 $1274万
 $23,640/呎
-(24年-07月-17日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -36678,7 +36678,7 @@
           <t>E | 488呎 (2房)
 $1158万
 $23,732/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -36686,7 +36686,7 @@
           <t>F | 555呎 (2房)
 $1365万
 $24,589/呎
-(24年-06月-27日)</t>
+(24年-06月)</t>
         </is>
       </c>
     </row>
@@ -36701,7 +36701,7 @@
           <t>A | 783呎 (3房)
 $2010万
 $25,676/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -36717,7 +36717,7 @@
           <t>C | 388呎 (1房)
 $800万
 $20,624/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -36725,7 +36725,7 @@
           <t>D | 539呎 (2房)
 $1262万
 $23,410/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -36733,7 +36733,7 @@
           <t>E | 488呎 (2房)
 $1147万
 $23,500/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -36741,7 +36741,7 @@
           <t>F | 555呎 (2房)
 $1371万
 $24,703/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -36756,7 +36756,7 @@
           <t>A | 783呎 (3房)
 $1953万
 $24,941/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -36764,7 +36764,7 @@
           <t>B | 536呎 (2房)
 $1316万
 $24,547/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -36772,7 +36772,7 @@
           <t>C | 388呎 (1房)
 $799万
 $20,582/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -36780,7 +36780,7 @@
           <t>D | 539呎 (2房)
 $1280万
 $23,746/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -36788,7 +36788,7 @@
           <t>E | 488呎 (2房)
 $1163万
 $23,838/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -36796,7 +36796,7 @@
           <t>F | 555呎 (2房)
 $1344万
 $24,223/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -36811,7 +36811,7 @@
           <t>A | 783呎 (3房)
 $1991万
 $25,425/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -36819,7 +36819,7 @@
           <t>B | 536呎 (2房)
 $1278万
 $23,845/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -36827,7 +36827,7 @@
           <t>C | 388呎 (1房)
 $817万
 $21,046/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -36835,7 +36835,7 @@
           <t>D | 539呎 (2房)
 $1237万
 $22,954/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -36843,7 +36843,7 @@
           <t>E | 488呎 (2房)
 $1152万
 $23,609/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -36851,7 +36851,7 @@
           <t>F | 555呎 (2房)
 $1318万
 $23,755/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -36866,7 +36866,7 @@
           <t>A | 783呎 (3房)
 $1943万
 $24,820/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -36874,7 +36874,7 @@
           <t>B | 536呎 (2房)
 $1278万
 $23,845/呎
-(24年-06月-23日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -36882,7 +36882,7 @@
           <t>C | 388呎 (1房)
 $797万
 $20,544/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -36890,7 +36890,7 @@
           <t>D | 539呎 (2房)
 $1237万
 $22,954/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -36898,7 +36898,7 @@
           <t>E | 488呎 (2房)
 $1125万
 $23,045/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -36906,7 +36906,7 @@
           <t>F | 555呎 (2房)
 $1306万
 $23,524/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -36921,7 +36921,7 @@
           <t>A | 783呎 (3房)
 $1924万
 $24,579/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -36929,7 +36929,7 @@
           <t>B | 536呎 (2房)
 $1266万
 $23,612/呎
-(24年-06月-03日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -36937,7 +36937,7 @@
           <t>C | 388呎 (1房)
 $792万
 $20,399/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -36945,7 +36945,7 @@
           <t>D | 539呎 (2房)
 $1255万
 $23,284/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -36953,7 +36953,7 @@
           <t>E | 488呎 (2房)
 $1141万
 $23,375/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -36961,7 +36961,7 @@
           <t>F | 555呎 (2房)
 $1238万
 $22,305/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -36976,7 +36976,7 @@
           <t>A | 783呎 (3房)
 $1962万
 $25,055/呎
-(24年-06月-25日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -36992,7 +36992,7 @@
           <t>C | 388呎 (1房)
 $790万
 $20,361/呎
-(24年-06月-27日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -37000,7 +37000,7 @@
           <t>D | 539呎 (2房)
 $1219万
 $22,620/呎
-(24年-06月-25日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -37008,7 +37008,7 @@
           <t>E | 488呎 (2房)
 $1115万
 $22,848/呎
-(24年-10月-17日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -37016,7 +37016,7 @@
           <t>F | 555呎 (2房)
 $1244万
 $22,405/呎
-(24年-06月-25日)</t>
+(24年-06月)</t>
         </is>
       </c>
     </row>
@@ -37031,7 +37031,7 @@
           <t>A | 783呎 (3房)
 $1906万
 $24,340/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -37047,7 +37047,7 @@
           <t>C | 388呎 (1房)
 $808万
 $20,817/呎
-(24年-07月-03日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -37055,7 +37055,7 @@
           <t>D | 539呎 (2房)
 $1272万
 $23,607/呎
-(24年-06月-24日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -37063,7 +37063,7 @@
           <t>E | 488呎 (2房)
 $1103万
 $22,596/呎
-(24年-06月-24日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -37071,7 +37071,7 @@
           <t>F | 555呎 (2房)
 $1211万
 $21,825/呎
-(24年-07月-03日)</t>
+(24年-07月)</t>
         </is>
       </c>
     </row>
@@ -37086,7 +37086,7 @@
           <t>A | 783呎 (3房)
 $1896万
 $24,221/呎
-(24年-06月-27日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -37102,7 +37102,7 @@
           <t>C | 388呎 (1房)
 $806万
 $20,773/呎
-(24年-07月-01日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -37110,7 +37110,7 @@
           <t>D | 539呎 (2房)
 $1207万
 $22,397/呎
-(24年-06月-27日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -37118,7 +37118,7 @@
           <t>E | 488呎 (2房)
 $1124万
 $23,035/呎
-(24年-06月-27日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -37126,7 +37126,7 @@
           <t>F | 555呎 (2房)
 $1205万
 $21,717/呎
-(24年-06月-27日)</t>
+(24年-06月)</t>
         </is>
       </c>
     </row>
@@ -37141,7 +37141,7 @@
           <t>A | 783呎 (3房)
 $1869万
 $23,870/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -37157,7 +37157,7 @@
           <t>C | 388呎 (1房)
 $778万
 $20,041/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -37165,7 +37165,7 @@
           <t>D | 539呎 (2房)
 $1231万
 $22,831/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -37173,7 +37173,7 @@
           <t>E | 488呎 (2房)
 $1119万
 $22,922/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -37181,7 +37181,7 @@
           <t>F | 555呎 (2房)
 $1171万
 $21,095/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -37196,7 +37196,7 @@
           <t>A | 783呎 (3房)
 $1887万
 $24,098/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -37212,7 +37212,7 @@
           <t>C | 388呎 (1房)
 $787万
 $20,289/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -37220,7 +37220,7 @@
           <t>D | 539呎 (2房)
 $1225万
 $22,720/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -37228,7 +37228,7 @@
           <t>E | 488呎 (2房)
 $1087万
 $22,266/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -37236,7 +37236,7 @@
           <t>F | 555呎 (2房)
 $1165万
 $20,993/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -37251,7 +37251,7 @@
           <t>A | 783呎 (3房)
 $1860万
 $23,750/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -37267,7 +37267,7 @@
           <t>C | 388呎 (1房)
 $759万
 $19,570/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -37275,7 +37275,7 @@
           <t>D | 539呎 (2房)
 $1219万
 $22,609/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -37283,7 +37283,7 @@
           <t>E | 488呎 (2房)
 $1108万
 $22,699/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -37291,7 +37291,7 @@
           <t>F | 555呎 (2房)
 $1188万
 $21,400/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -37306,7 +37306,7 @@
           <t>A | 783呎 (3房)
 $1798万
 $22,959/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -37314,7 +37314,7 @@
           <t>B | 536呎 (2房)
 $1210万
 $22,584/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -37322,7 +37322,7 @@
           <t>C | 388呎 (1房)
 $752万
 $19,379/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -37330,7 +37330,7 @@
           <t>D | 539呎 (2房)
 $1219万
 $22,609/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -37338,7 +37338,7 @@
           <t>E | 488呎 (2房)
 $1108万
 $22,699/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -37346,7 +37346,7 @@
           <t>F | 555呎 (2房)
 $1188万
 $21,400/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -37361,7 +37361,7 @@
           <t>A | 783呎 (3房)
 $1806万
 $23,068/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -37377,7 +37377,7 @@
           <t>C | 388呎 (1房)
 $757万
 $19,521/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -37385,7 +37385,7 @@
           <t>D | 539呎 (2房)
 $1178万
 $21,855/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -37393,7 +37393,7 @@
           <t>E | 488呎 (2房)
 $1097万
 $22,480/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -37401,7 +37401,7 @@
           <t>F | 555呎 (2房)
 $1148万
 $20,686/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -37416,7 +37416,7 @@
           <t>A | 783呎 (3房)
 $1797万
 $22,955/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -37432,7 +37432,7 @@
           <t>C | 388呎 (1房)
 $756万
 $19,482/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -37440,7 +37440,7 @@
           <t>D | 539呎 (2房)
 $1201万
 $22,278/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -37448,7 +37448,7 @@
           <t>E | 488呎 (2房)
 $1066万
 $21,834/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -37456,7 +37456,7 @@
           <t>F | 555呎 (2房)
 $1142万
 $20,584/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -37471,7 +37471,7 @@
           <t>A | 783呎 (3房)
 $1789万
 $22,844/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -37487,7 +37487,7 @@
           <t>C | 388呎 (1房)
 $754万
 $19,446/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -37495,7 +37495,7 @@
           <t>D | 539呎 (2房)
 $1166万
 $21,640/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -37503,7 +37503,7 @@
           <t>E | 488呎 (2房)
 $1060万
 $21,727/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -37511,7 +37511,7 @@
           <t>F | 555呎 (2房)
 $1137万
 $20,483/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -37542,7 +37542,7 @@
           <t>C | 388呎 (1房)
 $735万
 $18,943/呎
-(24年-06月-02日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -37550,7 +37550,7 @@
           <t>D | 539呎 (2房)
 $1189万
 $22,059/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -37558,7 +37558,7 @@
           <t>E | 488呎 (2房)
 $1055万
 $21,621/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -37566,7 +37566,7 @@
           <t>F | 555呎 (2房)
 $1131万
 $20,384/呎
-(24年-06月-02日)</t>
+(24年-06月)</t>
         </is>
       </c>
     </row>
@@ -37597,7 +37597,7 @@
           <t>C | 388呎 (1房)
 $734万
 $18,905/呎
-(24年-06月-04日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -37605,7 +37605,7 @@
           <t>D | 539呎 (2房)
 $1155万
 $21,429/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -37613,7 +37613,7 @@
           <t>E | 488呎 (2房)
 $1050万
 $21,516/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -37621,7 +37621,7 @@
           <t>F | 555呎 (2房)
 $1126万
 $20,283/呎
-(24年-05月-30日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -37636,7 +37636,7 @@
           <t>A | 740呎 (3房)
 $1934万
 $26,134/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -37644,7 +37644,7 @@
           <t>B | 498呎 (2房)
 $1219万
 $24,474/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -37660,7 +37660,7 @@
           <t>D | 502呎 (2房)
 $1231万
 $24,518/呎
-(24年-06月-04日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -37668,7 +37668,7 @@
           <t>E | 450呎 (2房)
 $1120万
 $24,889/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -37676,7 +37676,7 @@
           <t>F | 517呎 (2房)
 $1171万
 $22,646/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -37835,7 +37835,7 @@
           <t>C | 387呎 (1房)
 $856万
 $22,106/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -37843,7 +37843,7 @@
           <t>D | 377呎 (1房)
 $858万
 $22,772/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -37851,7 +37851,7 @@
           <t>E | 377呎 (1房)
 $836万
 $22,175/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -37859,7 +37859,7 @@
           <t>F | 525呎 (2房)
 $1402万
 $26,709/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -37874,7 +37874,7 @@
           <t>A | 757呎 (3房)
 $1970万
 $26,026/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -37890,7 +37890,7 @@
           <t>C | 387呎 (1房)
 $799万
 $20,651/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -37898,7 +37898,7 @@
           <t>D | 377呎 (1房)
 $801万
 $21,249/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -37906,7 +37906,7 @@
           <t>E | 378呎 (1房)
 $780万
 $20,638/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -37914,7 +37914,7 @@
           <t>F | 525呎 (2房)
 $1244万
 $23,688/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -37929,7 +37929,7 @@
           <t>A | 757呎 (3房)
 $2046万
 $27,032/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -37937,7 +37937,7 @@
           <t>B | 521呎 (2房)
 $1354万
 $25,983/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -37945,7 +37945,7 @@
           <t>C | 387呎 (1房)
 $798万
 $20,610/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -37953,7 +37953,7 @@
           <t>D | 377呎 (1房)
 $800万
 $21,207/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -37961,7 +37961,7 @@
           <t>E | 377呎 (1房)
 $779万
 $20,653/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -37969,7 +37969,7 @@
           <t>F | 525呎 (2房)
 $1268万
 $24,145/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -37984,7 +37984,7 @@
           <t>A | 757呎 (3房)
 $1960万
 $25,896/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -37992,7 +37992,7 @@
           <t>B | 521呎 (2房)
 $1296万
 $24,871/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -38000,7 +38000,7 @@
           <t>C | 387呎 (1房)
 $807万
 $20,863/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -38008,7 +38008,7 @@
           <t>D | 377呎 (1房)
 $790万
 $20,958/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -38016,7 +38016,7 @@
           <t>E | 377呎 (1房)
 $788万
 $20,907/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -38024,7 +38024,7 @@
           <t>F | 525呎 (2房)
 $1219万
 $23,223/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -38039,7 +38039,7 @@
           <t>A | 757呎 (3房)
 $1895万
 $25,033/呎
-(24年-06月-25日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -38047,7 +38047,7 @@
           <t>B | 521呎 (2房)
 $1283万
 $24,628/呎
-(24年-09月-10日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -38055,7 +38055,7 @@
           <t>C | 387呎 (1房)
 $787万
 $20,326/呎
-(24年-06月-24日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -38063,7 +38063,7 @@
           <t>D | 377呎 (1房)
 $770万
 $20,416/呎
-(24年-06月-25日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -38071,7 +38071,7 @@
           <t>E | 377呎 (1房)
 $768万
 $20,369/呎
-(24年-06月-25日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -38079,7 +38079,7 @@
           <t>F | 525呎 (2房)
 $1213万
 $23,109/呎
-(24年-06月-24日)</t>
+(24年-06月)</t>
         </is>
       </c>
     </row>
@@ -38094,7 +38094,7 @@
           <t>A | 757呎 (3房)
 $1922万
 $25,394/呎
-(24年-06月-27日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -38102,7 +38102,7 @@
           <t>B | 521呎 (2房)
 $1271万
 $24,388/呎
-(24年-09月-10日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -38110,7 +38110,7 @@
           <t>C | 387呎 (1房)
 $804万
 $20,780/呎
-(24年-06月-27日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -38118,7 +38118,7 @@
           <t>D | 377呎 (1房)
 $768万
 $20,377/呎
-(24年-06月-27日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -38126,7 +38126,7 @@
           <t>E | 377呎 (1房)
 $766万
 $20,329/呎
-(24年-07月-02日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -38134,7 +38134,7 @@
           <t>F | 525呎 (2房)
 $1207万
 $22,992/呎
-(24年-06月-27日)</t>
+(24年-06月)</t>
         </is>
       </c>
     </row>
@@ -38149,7 +38149,7 @@
           <t>A | 757呎 (3房)
 $1904万
 $25,148/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -38157,7 +38157,7 @@
           <t>B | 521呎 (2房)
 $1258万
 $24,150/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -38165,7 +38165,7 @@
           <t>C | 387呎 (1房)
 $784万
 $20,245/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -38173,7 +38173,7 @@
           <t>D | 377呎 (1房)
 $785万
 $20,833/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -38181,7 +38181,7 @@
           <t>E | 377呎 (1房)
 $765万
 $20,289/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -38189,7 +38189,7 @@
           <t>F | 525呎 (2房)
 $1206万
 $22,981/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -38204,7 +38204,7 @@
           <t>A | 757呎 (3房)
 $1840万
 $24,312/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -38212,7 +38212,7 @@
           <t>B | 521呎 (2房)
 $1276万
 $24,497/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -38220,7 +38220,7 @@
           <t>C | 387呎 (1房)
 $801万
 $20,700/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -38228,7 +38228,7 @@
           <t>D | 377呎 (1房)
 $803万
 $21,289/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -38236,7 +38236,7 @@
           <t>E | 377呎 (1房)
 $763万
 $20,247/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -38244,7 +38244,7 @@
           <t>F | 525呎 (2房)
 $1172万
 $22,324/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -38259,7 +38259,7 @@
           <t>A | 757呎 (3房)
 $1867万
 $24,663/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -38267,7 +38267,7 @@
           <t>B | 521呎 (2房)
 $1234万
 $23,681/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -38275,7 +38275,7 @@
           <t>C | 387呎 (1房)
 $780万
 $20,165/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -38283,15 +38283,15 @@
           <t>D | 377呎 (1房)
 $764万
 $20,255/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
         <is>
-          <t>E | 377呎 (1房)
+          <t>E | 378呎 (1房)
 $780万
-$20,700/呎
-(24年-05月-28日)</t>
+$20,646/呎
+(24年-05月)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -38299,7 +38299,7 @@
           <t>F | 525呎 (2房)
 $1195万
 $22,754/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -38314,7 +38314,7 @@
           <t>A | 757呎 (3房)
 $1822万
 $24,074/呎
-(24年-05月-30日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -38322,7 +38322,7 @@
           <t>B | 521呎 (2房)
 $1234万
 $23,681/呎
-(24年-05月-30日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -38330,7 +38330,7 @@
           <t>C | 387呎 (1房)
 $780万
 $20,165/呎
-(24年-05月-30日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -38338,7 +38338,7 @@
           <t>D | 377呎 (1房)
 $782万
 $20,748/呎
-(24年-05月-30日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -38346,7 +38346,7 @@
           <t>E | 377呎 (1房)
 $799万
 $21,191/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -38354,7 +38354,7 @@
           <t>F | 524呎 (2房)
 $1195万
 $22,798/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -38369,7 +38369,7 @@
           <t>A | 757呎 (3房)
 $1762万
 $23,273/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -38377,7 +38377,7 @@
           <t>B | 521呎 (2房)
 $1252万
 $24,021/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -38385,7 +38385,7 @@
           <t>C | 387呎 (1房)
 $794万
 $20,514/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -38393,7 +38393,7 @@
           <t>D | 377呎 (1房)
 $777万
 $20,607/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -38401,7 +38401,7 @@
           <t>E | 378呎 (1房)
 $757万
 $20,016/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -38409,7 +38409,7 @@
           <t>F | 525呎 (2房)
 $1155万
 $21,994/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -38424,7 +38424,7 @@
           <t>A | 757呎 (3房)
 $1753万
 $23,160/呎
-(24年-07月-01日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -38432,7 +38432,7 @@
           <t>B | 521呎 (2房)
 $1216万
 $23,334/呎
-(24年-06月-26日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -38440,7 +38440,7 @@
           <t>C | 388呎 (1房)
 $774万
 $19,936/呎
-(24年-07月-02日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -38448,7 +38448,7 @@
           <t>D | 377呎 (1房)
 $757万
 $20,077/呎
-(24年-07月-02日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -38456,7 +38456,7 @@
           <t>E | 377呎 (1房)
 $755万
 $20,029/呎
-(24年-07月-01日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -38464,7 +38464,7 @@
           <t>F | 525呎 (2房)
 $1149万
 $21,884/呎
-(24年-07月-01日)</t>
+(24年-07月)</t>
         </is>
       </c>
     </row>
@@ -38479,7 +38479,7 @@
           <t>A | 757呎 (3房)
 $1745万
 $23,048/呎
-(24年-06月-25日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -38487,7 +38487,7 @@
           <t>B | 521呎 (2房)
 $1210万
 $23,221/呎
-(24年-06月-26日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -38495,7 +38495,7 @@
           <t>C | 387呎 (1房)
 $772万
 $19,946/呎
-(24年-06月-26日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -38503,7 +38503,7 @@
           <t>D | 377呎 (1房)
 $774万
 $20,525/呎
-(24年-08月-11日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -38511,7 +38511,7 @@
           <t>E | 377呎 (1房)
 $754万
 $19,989/呎
-(24年-06月-25日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -38519,7 +38519,7 @@
           <t>F | 525呎 (2房)
 $1143万
 $21,777/呎
-(24年-06月-25日)</t>
+(24年-06月)</t>
         </is>
       </c>
     </row>
@@ -38534,7 +38534,7 @@
           <t>A | 757呎 (3房)
 $1736万
 $22,935/呎
-(24年-07月-01日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -38542,7 +38542,7 @@
           <t>B | 521呎 (2房)
 $1233万
 $23,668/呎
-(24年-07月-10日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -38550,7 +38550,7 @@
           <t>C | 387呎 (1房)
 $789万
 $20,393/呎
-(24年-07月-01日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -38558,7 +38558,7 @@
           <t>D | 377呎 (1房)
 $754万
 $19,997/呎
-(24年-08月-18日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -38566,7 +38566,7 @@
           <t>E | 377呎 (1房)
 $752万
 $19,950/呎
-(24年-07月-24日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -38574,7 +38574,7 @@
           <t>F | 525呎 (2房)
 $1138万
 $21,669/呎
-(24年-07月-01日)</t>
+(24年-07月)</t>
         </is>
       </c>
     </row>
@@ -38589,7 +38589,7 @@
           <t>A | 757呎 (3房)
 $1728万
 $22,823/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -38597,7 +38597,7 @@
           <t>B | 521呎 (2房)
 $1227万
 $23,555/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -38605,7 +38605,7 @@
           <t>C | 387呎 (1房)
 $761万
 $19,672/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -38613,7 +38613,7 @@
           <t>D | 377呎 (1房)
 $763万
 $20,241/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -38621,7 +38621,7 @@
           <t>E | 377呎 (1房)
 $761万
 $20,194/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -38629,7 +38629,7 @@
           <t>F | 525呎 (2房)
 $1121万
 $21,349/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -38644,7 +38644,7 @@
           <t>A | 757呎 (3房)
 $1761万
 $23,266/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -38652,7 +38652,7 @@
           <t>B | 521呎 (2房)
 $1221万
 $23,440/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -38660,7 +38660,7 @@
           <t>C | 387呎 (1房)
 $752万
 $19,442/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -38668,7 +38668,7 @@
           <t>D | 377呎 (1房)
 $736万
 $19,528/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -38676,7 +38676,7 @@
           <t>E | 377呎 (1房)
 $752万
 $19,955/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -38684,7 +38684,7 @@
           <t>F | 525呎 (2房)
 $1104万
 $21,034/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -38699,7 +38699,7 @@
           <t>A | 757呎 (3房)
 $1711万
 $22,601/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -38707,7 +38707,7 @@
           <t>B | 521呎 (2房)
 $1186万
 $22,768/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -38715,7 +38715,7 @@
           <t>C | 387呎 (1房)
 $762万
 $19,680/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -38723,7 +38723,7 @@
           <t>D | 377呎 (1房)
 $728万
 $19,297/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -38731,7 +38731,7 @@
           <t>E | 377呎 (1房)
 $726万
 $19,252/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -38739,7 +38739,7 @@
           <t>F | 525呎 (2房)
 $1088万
 $20,726/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -38754,7 +38754,7 @@
           <t>A | 757呎 (3房)
 $1711万
 $22,601/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -38762,7 +38762,7 @@
           <t>B | 521呎 (2房)
 $1186万
 $22,768/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -38770,7 +38770,7 @@
           <t>C | 388呎 (1房)
 $736万
 $18,974/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -38778,7 +38778,7 @@
           <t>D | 378呎 (1房)
 $738万
 $19,521/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -38786,7 +38786,7 @@
           <t>E | 377呎 (1房)
 $754万
 $19,989/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -38794,7 +38794,7 @@
           <t>F | 524呎 (2房)
 $1104万
 $21,063/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -38809,7 +38809,7 @@
           <t>A | 757呎 (3房)
 $1694万
 $22,383/呎
-(24年-05月-30日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -38817,7 +38817,7 @@
           <t>B | 521呎 (2房)
 $1175万
 $22,545/呎
-(24年-05月-30日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -38825,7 +38825,7 @@
           <t>C | 387呎 (1房)
 $724万
 $18,705/呎
-(24年-05月-30日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -38833,7 +38833,7 @@
           <t>D | 377呎 (1房)
 $726万
 $19,249/呎
-(24年-05月-30日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -38841,7 +38841,7 @@
           <t>E | 377呎 (1房)
 $724万
 $19,202/呎
-(24年-05月-30日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -38849,7 +38849,7 @@
           <t>F | 525呎 (2房)
 $1056万
 $20,120/呎
-(24年-05月-30日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -38864,7 +38864,7 @@
           <t>A | 757呎 (3房)
 $1686万
 $22,273/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -38872,7 +38872,7 @@
           <t>B | 521呎 (2房)
 $1169万
 $22,436/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -38880,7 +38880,7 @@
           <t>C | 387呎 (1房)
 $722万
 $18,669/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -38888,7 +38888,7 @@
           <t>D | 377呎 (1房)
 $724万
 $19,210/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -38896,7 +38896,7 @@
           <t>E | 377呎 (1房)
 $705万
 $18,708/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -38904,7 +38904,7 @@
           <t>F | 525呎 (2房)
 $1051万
 $20,021/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -38919,7 +38919,7 @@
           <t>A | 757呎 (3房)
 $1678万
 $22,165/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -38927,7 +38927,7 @@
           <t>B | 521呎 (2房)
 $1192万
 $22,869/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -38935,7 +38935,7 @@
           <t>C | 387呎 (1房)
 $739万
 $19,088/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -38943,7 +38943,7 @@
           <t>D | 377呎 (1房)
 $706万
 $18,716/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -38951,7 +38951,7 @@
           <t>E | 377呎 (1房)
 $704万
 $18,671/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -38959,7 +38959,7 @@
           <t>F | 525呎 (2房)
 $1071万
 $20,408/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -38974,7 +38974,7 @@
           <t>A | 757呎 (3房)
 $1670万
 $22,058/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -38982,7 +38982,7 @@
           <t>B | 521呎 (2房)
 $1186万
 $22,758/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -38990,7 +38990,7 @@
           <t>C | 387呎 (1房)
 $737万
 $19,049/呎
-(24年-06月-04日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -38998,7 +38998,7 @@
           <t>D | 377呎 (1房)
 $704万
 $18,679/呎
-(24年-06月-06日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -39006,7 +39006,7 @@
           <t>E | 377呎 (1房)
 $702万
 $18,634/呎
-(24年-06月-02日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -39014,7 +39014,7 @@
           <t>F | 525呎 (2房)
 $1041万
 $19,823/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -39029,7 +39029,7 @@
           <t>A | 757呎 (3房)
 $1702万
 $22,485/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -39037,7 +39037,7 @@
           <t>B | 521呎 (2房)
 $1152万
 $22,107/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -39045,7 +39045,7 @@
           <t>C | 387呎 (1房)
 $718万
 $18,558/呎
-(24年-06月-20日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -39053,7 +39053,7 @@
           <t>D | 377呎 (1房)
 $703万
 $18,642/呎
-(24年-06月-11日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -39061,7 +39061,7 @@
           <t>E | 377呎 (1房)
 $718万
 $19,050/呎
-(24年-06月-04日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -39069,7 +39069,7 @@
           <t>F | 525呎 (2房)
 $1036万
 $19,726/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -39084,7 +39084,7 @@
           <t>A | 716呎 (3房)
 $1769万
 $24,707/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -39092,7 +39092,7 @@
           <t>B | 481呎 (2房)
 $1196万
 $24,871/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -39100,7 +39100,7 @@
           <t>C | 350呎 (1房)
 $753万
 $21,509/呎
-(24年-06月-04日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -39108,7 +39108,7 @@
           <t>D | 340呎 (1房)
 $732万
 $21,532/呎
-(24年-06月-04日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -39116,7 +39116,7 @@
           <t>E | 340呎 (1房)
 $748万
 $22,003/呎
-(24年-05月-25日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -39124,7 +39124,7 @@
           <t>F | 487呎 (2房)
 $1140万
 $23,405/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -39282,7 +39282,7 @@
           <t>B | 761呎 (3房)
 $1960万
 $25,761/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -39290,7 +39290,7 @@
           <t>C | 497呎 (2房)
 $1289万
 $25,932/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -39298,7 +39298,7 @@
           <t>D | 388呎 (1房)
 $863万
 $22,250/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -39306,7 +39306,7 @@
           <t>E | 391呎 (1房)
 $858万
 $21,944/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr"/>
@@ -39322,7 +39322,7 @@
           <t>A | 774呎 (3房)
 $2051万
 $26,497/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -39330,7 +39330,7 @@
           <t>B | 760呎 (3房)
 $1859万
 $24,455/呎
-(24年-06月-03日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -39338,7 +39338,7 @@
           <t>C | 497呎 (2房)
 $1142万
 $22,978/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -39346,7 +39346,7 @@
           <t>D | 388呎 (1房)
 $789万
 $20,330/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -39354,7 +39354,7 @@
           <t>E | 388呎 (1房)
 $808万
 $20,812/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -39362,7 +39362,7 @@
           <t>F | 528呎 (2房)
 $1334万
 $25,263/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -39377,7 +39377,7 @@
           <t>A | 774呎 (3房)
 $2030万
 $26,234/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -39385,7 +39385,7 @@
           <t>B | 760呎 (3房)
 $1849万
 $24,334/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -39393,7 +39393,7 @@
           <t>C | 497呎 (2房)
 $1136万
 $22,865/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -39401,7 +39401,7 @@
           <t>D | 388呎 (1房)
 $787万
 $20,289/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -39409,7 +39409,7 @@
           <t>E | 388呎 (1房)
 $773万
 $19,925/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -39417,7 +39417,7 @@
           <t>F | 528呎 (2房)
 $1321万
 $25,013/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -39432,7 +39432,7 @@
           <t>A | 774呎 (3房)
 $1991万
 $25,720/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -39440,7 +39440,7 @@
           <t>B | 760呎 (3房)
 $1779万
 $23,408/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -39448,7 +39448,7 @@
           <t>C | 497呎 (2房)
 $1147万
 $23,082/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -39456,7 +39456,7 @@
           <t>D | 388呎 (1房)
 $797万
 $20,544/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -39464,7 +39464,7 @@
           <t>E | 388呎 (1房)
 $758万
 $19,526/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -39472,7 +39472,7 @@
           <t>F | 528呎 (2房)
 $1264万
 $23,939/呎
-(24年-05月-30日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -39487,7 +39487,7 @@
           <t>A | 774呎 (3房)
 $1924万
 $24,859/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -39495,7 +39495,7 @@
           <t>B | 760呎 (3房)
 $1813万
 $23,861/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -39503,7 +39503,7 @@
           <t>C | 497呎 (2房)
 $1142万
 $22,970/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -39511,7 +39511,7 @@
           <t>D | 388呎 (1房)
 $796万
 $20,503/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -39519,7 +39519,7 @@
           <t>E | 388呎 (1房)
 $745万
 $19,201/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -39527,7 +39527,7 @@
           <t>F | 528呎 (2房)
 $1252万
 $23,703/呎
-(24年-06月-12日)</t>
+(24年-06月)</t>
         </is>
       </c>
     </row>
@@ -39542,7 +39542,7 @@
           <t>A | 774呎 (3房)
 $1961万
 $25,339/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -39550,7 +39550,7 @@
           <t>B | 760呎 (3房)
 $1762万
 $23,178/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -39558,7 +39558,7 @@
           <t>C | 497呎 (2房)
 $1136万
 $22,855/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -39566,7 +39566,7 @@
           <t>D | 388呎 (1房)
 $794万
 $20,461/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -39574,7 +39574,7 @@
           <t>E | 389呎 (1房)
 $752万
 $19,332/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -39582,7 +39582,7 @@
           <t>F | 528呎 (2房)
 $1276万
 $24,161/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -39597,7 +39597,7 @@
           <t>A | 774呎 (3房)
 $1952万
 $25,213/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -39605,7 +39605,7 @@
           <t>B | 760呎 (3房)
 $1796万
 $23,626/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -39613,7 +39613,7 @@
           <t>C | 497呎 (2房)
 $1130万
 $22,744/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -39621,7 +39621,7 @@
           <t>D | 388呎 (1房)
 $792万
 $20,423/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -39629,7 +39629,7 @@
           <t>E | 388呎 (1房)
 $727万
 $18,727/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -39637,7 +39637,7 @@
           <t>F | 528呎 (2房)
 $1239万
 $23,468/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -39652,7 +39652,7 @@
           <t>A | 774呎 (3房)
 $1942万
 $25,087/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -39660,7 +39660,7 @@
           <t>B | 760呎 (3房)
 $1787万
 $23,511/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -39668,7 +39668,7 @@
           <t>C | 497呎 (2房)
 $1125万
 $22,632/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -39676,7 +39676,7 @@
           <t>D | 392呎 (1房)
 $772万
 $19,694/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -39684,7 +39684,7 @@
           <t>E | 388呎 (1房)
 $725万
 $18,691/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -39692,7 +39692,7 @@
           <t>F | 528呎 (2房)
 $1263万
 $23,919/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -39707,7 +39707,7 @@
           <t>A | 774呎 (3房)
 $1849万
 $23,893/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -39715,7 +39715,7 @@
           <t>B | 760呎 (3房)
 $1778万
 $23,393/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -39723,7 +39723,7 @@
           <t>C | 497呎 (2房)
 $1119万
 $22,523/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -39731,7 +39731,7 @@
           <t>D | 388呎 (1房)
 $789万
 $20,343/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -39739,7 +39739,7 @@
           <t>E | 388呎 (1房)
 $724万
 $18,652/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -39747,7 +39747,7 @@
           <t>F | 528呎 (2房)
 $1257万
 $23,801/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -39762,7 +39762,7 @@
           <t>A | 774呎 (3房)
 $1813万
 $23,424/呎
-(24年-05月-13日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -39770,7 +39770,7 @@
           <t>B | 760呎 (3房)
 $1736万
 $22,837/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -39778,7 +39778,7 @@
           <t>C | 497呎 (2房)
 $1093万
 $21,986/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -39786,7 +39786,7 @@
           <t>D | 388呎 (1房)
 $770万
 $19,858/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -39794,7 +39794,7 @@
           <t>E | 388呎 (1房)
 $724万
 $18,652/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -39802,7 +39802,7 @@
           <t>F | 528呎 (2房)
 $1232万
 $23,333/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -39817,7 +39817,7 @@
           <t>A | 774呎 (3房)
 $1760万
 $22,742/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -39825,7 +39825,7 @@
           <t>B | 760呎 (3房)
 $1719万
 $22,613/呎
-(24年-05月-13日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -39833,7 +39833,7 @@
           <t>C | 497呎 (2房)
 $1082万
 $21,773/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -39841,7 +39841,7 @@
           <t>D | 388呎 (1房)
 $784万
 $20,204/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -39849,7 +39849,7 @@
           <t>E | 389呎 (1房)
 $719万
 $18,476/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -39857,7 +39857,7 @@
           <t>F | 528呎 (2房)
 $1168万
 $22,116/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -39872,7 +39872,7 @@
           <t>A | 774呎 (3房)
 $1759万
 $22,729/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -39880,7 +39880,7 @@
           <t>B | 760呎 (3房)
 $1752万
 $23,050/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -39888,7 +39888,7 @@
           <t>C | 497呎 (2房)
 $1103万
 $22,195/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -39896,7 +39896,7 @@
           <t>D | 388呎 (1房)
 $782万
 $20,162/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -39904,7 +39904,7 @@
           <t>E | 388呎 (1房)
 $735万
 $18,938/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -39912,7 +39912,7 @@
           <t>F | 528呎 (2房)
 $1167万
 $22,102/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -39927,7 +39927,7 @@
           <t>A | 774呎 (3房)
 $1716万
 $22,174/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -39935,7 +39935,7 @@
           <t>B | 760呎 (3房)
 $1702万
 $22,391/呎
-(24年-10月-22日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -39943,7 +39943,7 @@
           <t>C | 497呎 (2房)
 $1098万
 $22,085/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -39951,7 +39951,7 @@
           <t>D | 388呎 (1房)
 $781万
 $20,124/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -39959,7 +39959,7 @@
           <t>E | 388呎 (1房)
 $733万
 $18,897/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -39967,7 +39967,7 @@
           <t>F | 528呎 (2房)
 $1139万
 $21,564/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -39982,7 +39982,7 @@
           <t>A | 774呎 (3房)
 $1635万
 $21,119/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -39990,7 +39990,7 @@
           <t>B | 760呎 (3房)
 $1735万
 $22,824/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -39998,7 +39998,7 @@
           <t>C | 497呎 (2房)
 $1066万
 $21,455/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -40006,7 +40006,7 @@
           <t>D | 388呎 (1房)
 $779万
 $20,085/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -40014,7 +40014,7 @@
           <t>E | 388呎 (1房)
 $714万
 $18,412/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -40022,7 +40022,7 @@
           <t>F | 528呎 (2房)
 $1111万
 $21,036/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40037,7 +40037,7 @@
           <t>A | 774呎 (3房)
 $1634万
 $21,106/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -40045,7 +40045,7 @@
           <t>B | 760呎 (3房)
 $1685万
 $22,171/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -40053,7 +40053,7 @@
           <t>C | 497呎 (2房)
 $1087万
 $21,869/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -40061,7 +40061,7 @@
           <t>D | 388呎 (1房)
 $778万
 $20,046/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -40069,7 +40069,7 @@
           <t>E | 388呎 (1房)
 $730万
 $18,825/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -40077,7 +40077,7 @@
           <t>F | 528呎 (2房)
 $1058万
 $20,036/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40092,7 +40092,7 @@
           <t>A | 774呎 (3房)
 $1593万
 $20,579/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -40100,7 +40100,7 @@
           <t>B | 760呎 (3房)
 $1677万
 $22,062/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -40108,7 +40108,7 @@
           <t>C | 497呎 (2房)
 $1056万
 $21,243/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -40116,7 +40116,7 @@
           <t>D | 388呎 (1房)
 $758万
 $19,531/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -40124,7 +40124,7 @@
           <t>E | 388呎 (1房)
 $712万
 $18,338/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -40132,7 +40132,7 @@
           <t>F | 528呎 (2房)
 $1061万
 $20,100/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40147,7 +40147,7 @@
           <t>A | 774呎 (3房)
 $1547万
 $19,988/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -40155,7 +40155,7 @@
           <t>B | 760呎 (3房)
 $1709万
 $22,488/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -40163,7 +40163,7 @@
           <t>C | 497呎 (2房)
 $1051万
 $21,141/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -40171,7 +40171,7 @@
           <t>D | 388呎 (1房)
 $756万
 $19,492/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -40179,7 +40179,7 @@
           <t>E | 388呎 (1房)
 $710万
 $18,302/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -40187,7 +40187,7 @@
           <t>F | 528呎 (2房)
 $1031万
 $19,525/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40202,7 +40202,7 @@
           <t>A | 774呎 (3房)
 $1547万
 $19,988/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -40210,7 +40210,7 @@
           <t>B | 760呎 (3房)
 $1668万
 $21,953/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -40218,7 +40218,7 @@
           <t>C | 497呎 (2房)
 $1051万
 $21,141/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -40226,7 +40226,7 @@
           <t>D | 388呎 (1房)
 $756万
 $19,492/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -40234,7 +40234,7 @@
           <t>E | 388呎 (1房)
 $710万
 $18,302/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -40242,7 +40242,7 @@
           <t>F | 528呎 (2房)
 $1056万
 $20,000/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40257,7 +40257,7 @@
           <t>A | 774呎 (3房)
 $1569万
 $20,273/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -40265,7 +40265,7 @@
           <t>B | 760呎 (3房)
 $1692万
 $22,268/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -40273,7 +40273,7 @@
           <t>C | 497呎 (2房)
 $1066万
 $21,447/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -40281,7 +40281,7 @@
           <t>D | 388呎 (1房)
 $769万
 $19,830/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -40289,7 +40289,7 @@
           <t>E | 388呎 (1房)
 $705万
 $18,175/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -40297,7 +40297,7 @@
           <t>F | 528呎 (2房)
 $1046万
 $19,803/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40312,7 +40312,7 @@
           <t>A | 774呎 (3房)
 $1561万
 $20,173/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -40320,7 +40320,7 @@
           <t>B | 760呎 (3房)
 $1684万
 $22,159/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -40328,7 +40328,7 @@
           <t>C | 497呎 (2房)
 $1042万
 $20,960/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -40336,7 +40336,7 @@
           <t>D | 388呎 (1房)
 $750万
 $19,322/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -40344,7 +40344,7 @@
           <t>E | 388呎 (1房)
 $704万
 $18,139/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -40352,7 +40352,7 @@
           <t>F | 528呎 (2房)
 $1040万
 $19,706/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40367,7 +40367,7 @@
           <t>A | 774呎 (3房)
 $1517万
 $19,594/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -40375,7 +40375,7 @@
           <t>B | 760呎 (3房)
 $1636万
 $21,525/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -40383,7 +40383,7 @@
           <t>C | 497呎 (2房)
 $1030万
 $20,730/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -40391,7 +40391,7 @@
           <t>D | 388呎 (1房)
 $748万
 $19,284/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -40399,7 +40399,7 @@
           <t>E | 388呎 (1房)
 $720万
 $18,544/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -40407,7 +40407,7 @@
           <t>F | 528呎 (2房)
 $1011万
 $19,140/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40422,7 +40422,7 @@
           <t>A | 774呎 (3房)
 $1509万
 $19,497/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -40430,7 +40430,7 @@
           <t>B | 760呎 (3房)
 $1628万
 $21,418/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -40438,7 +40438,7 @@
           <t>C | 497呎 (2房)
 $1025万
 $20,630/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -40446,7 +40446,7 @@
           <t>D | 388呎 (1房)
 $747万
 $19,245/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -40454,7 +40454,7 @@
           <t>E | 388呎 (1房)
 $718万
 $18,508/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -40462,7 +40462,7 @@
           <t>F | 528呎 (2房)
 $1030万
 $19,509/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40477,7 +40477,7 @@
           <t>A | 774呎 (3房)
 $1502万
 $19,401/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -40485,7 +40485,7 @@
           <t>B | 760呎 (3房)
 $1630万
 $21,443/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -40493,7 +40493,7 @@
           <t>C | 497呎 (2房)
 $1045万
 $21,030/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -40501,7 +40501,7 @@
           <t>D | 388呎 (1房)
 $764万
 $19,678/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -40509,7 +40509,7 @@
           <t>E | 388呎 (1房)
 $700万
 $18,031/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -40517,7 +40517,7 @@
           <t>F | 528呎 (2房)
 $1025万
 $19,413/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40532,7 +40532,7 @@
           <t>A | 732呎 (3房)
 $1570万
 $21,455/呎
-(24年-05月-13日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -40540,7 +40540,7 @@
           <t>B | 719呎 (3房)
 $1742万
 $24,224/呎
-(24年-05月-13日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -40548,7 +40548,7 @@
           <t>C | 459呎 (2房)
 $1062万
 $23,126/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -40556,7 +40556,7 @@
           <t>D | 350呎 (1房)
 $793万
 $22,651/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -40564,7 +40564,7 @@
           <t>E | 350呎 (1房)
 $756万
 $21,589/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -40572,7 +40572,7 @@
           <t>F | 490呎 (2房)
 $1068万
 $21,788/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40731,7 +40731,7 @@
           <t>C | 388呎 (1房)
 $812万
 $20,938/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -40739,7 +40739,7 @@
           <t>D | 377呎 (1房)
 $810万
 $21,475/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -40747,7 +40747,7 @@
           <t>E | 377呎 (1房)
 $794万
 $21,064/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -40755,7 +40755,7 @@
           <t>F | 525呎 (2房)
 $1259万
 $23,983/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40770,7 +40770,7 @@
           <t>A | 757呎 (3房)
 $1818万
 $24,011/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -40778,7 +40778,7 @@
           <t>B | 520呎 (2房)
 $1267万
 $24,363/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -40786,7 +40786,7 @@
           <t>C | 388呎 (1房)
 $776万
 $20,005/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -40794,7 +40794,7 @@
           <t>D | 377呎 (1房)
 $737万
 $19,557/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -40802,7 +40802,7 @@
           <t>E | 377呎 (1房)
 $759万
 $20,130/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -40810,7 +40810,7 @@
           <t>F | 525呎 (2房)
 $1143万
 $21,771/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40825,7 +40825,7 @@
           <t>A | 757呎 (3房)
 $1844万
 $24,354/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -40833,7 +40833,7 @@
           <t>B | 520呎 (2房)
 $1254万
 $24,123/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -40841,7 +40841,7 @@
           <t>C | 388呎 (1房)
 $765万
 $19,716/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -40849,7 +40849,7 @@
           <t>D | 377呎 (1房)
 $736万
 $19,517/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -40857,7 +40857,7 @@
           <t>E | 377呎 (1房)
 $757万
 $20,090/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -40865,7 +40865,7 @@
           <t>F | 525呎 (2房)
 $1165万
 $22,192/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40880,7 +40880,7 @@
           <t>A | 757呎 (3房)
 $1807万
 $23,876/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -40888,7 +40888,7 @@
           <t>B | 520呎 (2房)
 $1230万
 $23,648/呎
-(24年-05月-13日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -40896,7 +40896,7 @@
           <t>C | 388呎 (1房)
 $736万
 $18,961/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -40904,7 +40904,7 @@
           <t>D | 377呎 (1房)
 $727万
 $19,286/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -40912,7 +40912,7 @@
           <t>E | 377呎 (1房)
 $748万
 $19,851/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -40920,7 +40920,7 @@
           <t>F | 525呎 (2房)
 $1120万
 $21,343/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40935,7 +40935,7 @@
           <t>A | 757呎 (3房)
 $1747万
 $23,077/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -40943,7 +40943,7 @@
           <t>B | 520呎 (2房)
 $1218万
 $23,415/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -40951,7 +40951,7 @@
           <t>C | 388呎 (1房)
 $725万
 $18,680/呎
-(24年-05月-30日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -40959,7 +40959,7 @@
           <t>D | 377呎 (1房)
 $726万
 $19,249/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -40967,7 +40967,7 @@
           <t>E | 377呎 (1房)
 $729万
 $19,342/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -40975,7 +40975,7 @@
           <t>F | 525呎 (2房)
 $1142万
 $21,754/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40990,7 +40990,7 @@
           <t>A | 757呎 (3房)
 $1730万
 $22,848/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -40998,7 +40998,7 @@
           <t>B | 520呎 (2房)
 $1177万
 $22,631/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -41006,7 +41006,7 @@
           <t>C | 388呎 (1房)
 $735万
 $18,938/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -41014,7 +41014,7 @@
           <t>D | 377呎 (1房)
 $742万
 $19,682/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -41022,7 +41022,7 @@
           <t>E | 377呎 (1房)
 $728万
 $19,302/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -41030,7 +41030,7 @@
           <t>F | 525呎 (2房)
 $1136万
 $21,646/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41045,7 +41045,7 @@
           <t>A | 757呎 (3房)
 $1712万
 $22,622/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -41053,7 +41053,7 @@
           <t>B | 520呎 (2房)
 $1194万
 $22,954/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -41061,7 +41061,7 @@
           <t>C | 388呎 (1房)
 $716万
 $18,451/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -41069,7 +41069,7 @@
           <t>D | 377呎 (1房)
 $723万
 $19,172/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -41077,7 +41077,7 @@
           <t>E | 377呎 (1房)
 $726万
 $19,265/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -41085,7 +41085,7 @@
           <t>F | 525呎 (2房)
 $1082万
 $20,615/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41100,7 +41100,7 @@
           <t>A | 757呎 (3房)
 $1696万
 $22,398/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -41108,7 +41108,7 @@
           <t>B | 520呎 (2房)
 $1182万
 $22,725/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -41116,7 +41116,7 @@
           <t>C | 388呎 (1房)
 $714万
 $18,415/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -41124,7 +41124,7 @@
           <t>D | 377呎 (1房)
 $739万
 $19,602/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -41132,7 +41132,7 @@
           <t>E | 377呎 (1房)
 $743万
 $19,698/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -41140,7 +41140,7 @@
           <t>F | 525呎 (2房)
 $1077万
 $20,512/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41155,7 +41155,7 @@
           <t>A | 757呎 (3房)
 $1720万
 $22,716/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -41163,7 +41163,7 @@
           <t>B | 520呎 (2房)
 $1142万
 $21,965/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -41171,7 +41171,7 @@
           <t>C | 388呎 (1房)
 $713万
 $18,376/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -41179,7 +41179,7 @@
           <t>D | 377呎 (1房)
 $720万
 $19,098/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -41187,7 +41187,7 @@
           <t>E | 377呎 (1房)
 $723万
 $19,188/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -41195,7 +41195,7 @@
           <t>F | 525呎 (2房)
 $1072万
 $20,411/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41210,7 +41210,7 @@
           <t>A | 757呎 (3房)
 $1638万
 $21,635/呎
-(24年-05月-13日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -41218,7 +41218,7 @@
           <t>B | 520呎 (2房)
 $1170万
 $22,500/呎
-(24年-05月-13日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -41226,7 +41226,7 @@
           <t>C | 388呎 (1房)
 $713万
 $18,376/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -41234,7 +41234,7 @@
           <t>D | 377呎 (1房)
 $720万
 $19,098/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -41242,7 +41242,7 @@
           <t>E | 377呎 (1房)
 $741万
 $19,655/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -41250,7 +41250,7 @@
           <t>F | 525呎 (2房)
 $1098万
 $20,909/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41265,7 +41265,7 @@
           <t>A | 757呎 (3房)
 $1622万
 $21,421/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -41273,7 +41273,7 @@
           <t>B | 520呎 (2房)
 $1131万
 $21,748/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -41281,7 +41281,7 @@
           <t>C | 388呎 (1房)
 $725万
 $18,693/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -41289,7 +41289,7 @@
           <t>D | 377呎 (1房)
 $732万
 $19,430/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -41297,7 +41297,7 @@
           <t>E | 378呎 (1房)
 $736万
 $19,468/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -41305,7 +41305,7 @@
           <t>F | 525呎 (2房)
 $1087万
 $20,703/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41320,7 +41320,7 @@
           <t>A | 757呎 (3房)
 $1614万
 $21,314/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -41328,7 +41328,7 @@
           <t>B | 520呎 (2房)
 $1153万
 $22,165/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -41336,7 +41336,7 @@
           <t>C | 388呎 (1房)
 $724万
 $18,657/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -41344,7 +41344,7 @@
           <t>D | 377呎 (1房)
 $731万
 $19,390/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -41352,7 +41352,7 @@
           <t>E | 377呎 (1房)
 $717万
 $19,019/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -41360,7 +41360,7 @@
           <t>F | 525呎 (2房)
 $1081万
 $20,598/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41375,7 +41375,7 @@
           <t>A | 757呎 (3房)
 $1645万
 $21,725/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -41383,7 +41383,7 @@
           <t>B | 520呎 (2房)
 $1120万
 $21,533/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -41391,7 +41391,7 @@
           <t>C | 388呎 (1房)
 $705万
 $18,178/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -41399,7 +41399,7 @@
           <t>D | 377呎 (1房)
 $712万
 $18,891/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -41407,7 +41407,7 @@
           <t>E | 377呎 (1房)
 $716万
 $18,981/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -41415,7 +41415,7 @@
           <t>F | 525呎 (2房)
 $1050万
 $20,008/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41430,7 +41430,7 @@
           <t>A | 757呎 (3房)
 $1636万
 $21,618/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -41438,7 +41438,7 @@
           <t>B | 520呎 (2房)
 $1114万
 $21,425/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -41446,7 +41446,7 @@
           <t>C | 388呎 (1房)
 $721万
 $18,582/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -41454,7 +41454,7 @@
           <t>D | 377呎 (1房)
 $728万
 $19,310/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -41462,7 +41462,7 @@
           <t>E | 377呎 (1房)
 $732万
 $19,406/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -41470,7 +41470,7 @@
           <t>F | 525呎 (2房)
 $1071万
 $20,394/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41485,7 +41485,7 @@
           <t>A | 757呎 (3房)
 $1628万
 $21,510/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -41493,7 +41493,7 @@
           <t>B | 520呎 (2房)
 $1136万
 $21,837/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -41501,7 +41501,7 @@
           <t>C | 388呎 (1房)
 $702万
 $18,103/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -41509,7 +41509,7 @@
           <t>D | 377呎 (1房)
 $709万
 $18,814/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -41517,7 +41517,7 @@
           <t>E | 377呎 (1房)
 $713万
 $18,905/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -41525,7 +41525,7 @@
           <t>F | 524呎 (2房)
 $1040万
 $19,847/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41540,7 +41540,7 @@
           <t>A | 757呎 (3房)
 $1620万
 $21,403/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -41548,7 +41548,7 @@
           <t>B | 520呎 (2房)
 $1130万
 $21,729/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -41556,7 +41556,7 @@
           <t>C | 388呎 (1房)
 $701万
 $18,067/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -41564,7 +41564,7 @@
           <t>D | 377呎 (1房)
 $708万
 $18,777/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -41572,7 +41572,7 @@
           <t>E | 377呎 (1房)
 $729万
 $19,326/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -41580,7 +41580,7 @@
           <t>F | 525呎 (2房)
 $1060万
 $20,192/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41595,7 +41595,7 @@
           <t>A | 757呎 (3房)
 $1612万
 $21,297/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -41603,7 +41603,7 @@
           <t>B | 520呎 (2房)
 $1124万
 $21,621/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -41611,7 +41611,7 @@
           <t>C | 388呎 (1房)
 $700万
 $18,031/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -41619,7 +41619,7 @@
           <t>D | 377呎 (1房)
 $724万
 $19,196/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -41627,7 +41627,7 @@
           <t>E | 377呎 (1房)
 $710万
 $18,830/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -41635,7 +41635,7 @@
           <t>F | 525呎 (2房)
 $1055万
 $20,091/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41650,7 +41650,7 @@
           <t>A | 757呎 (3房)
 $1612万
 $21,297/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -41658,7 +41658,7 @@
           <t>B | 520呎 (2房)
 $1098万
 $21,106/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -41666,7 +41666,7 @@
           <t>C | 388呎 (1房)
 $734万
 $18,912/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -41674,7 +41674,7 @@
           <t>D | 377呎 (1房)
 $741万
 $19,655/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -41682,7 +41682,7 @@
           <t>E | 377呎 (1房)
 $710万
 $18,830/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -41690,7 +41690,7 @@
           <t>F | 525呎 (2房)
 $1030万
 $19,613/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41705,7 +41705,7 @@
           <t>A | 757呎 (3房)
 $1558万
 $20,584/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -41713,7 +41713,7 @@
           <t>B | 520呎 (2房)
 $1087万
 $20,898/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -41721,7 +41721,7 @@
           <t>C | 388呎 (1房)
 $695万
 $17,907/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -41729,7 +41729,7 @@
           <t>D | 377呎 (1房)
 $719万
 $19,064/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -41737,7 +41737,7 @@
           <t>E | 377呎 (1房)
 $722万
 $19,156/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -41745,7 +41745,7 @@
           <t>F | 525呎 (2房)
 $1020万
 $19,419/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41760,7 +41760,7 @@
           <t>A | 757呎 (3房)
 $1550万
 $20,481/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -41768,7 +41768,7 @@
           <t>B | 520呎 (2房)
 $1108万
 $21,302/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -41776,7 +41776,7 @@
           <t>C | 388呎 (1房)
 $710万
 $18,307/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -41784,7 +41784,7 @@
           <t>D | 377呎 (1房)
 $717万
 $19,027/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -41792,7 +41792,7 @@
           <t>E | 377呎 (1房)
 $721万
 $19,117/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -41800,7 +41800,7 @@
           <t>F | 525呎 (2房)
 $1039万
 $19,794/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41815,7 +41815,7 @@
           <t>A | 757呎 (3房)
 $1543万
 $20,379/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -41823,7 +41823,7 @@
           <t>B | 520呎 (2房)
 $1102万
 $21,196/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -41831,7 +41831,7 @@
           <t>C | 388呎 (1房)
 $709万
 $18,271/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -41839,7 +41839,7 @@
           <t>D | 377呎 (1房)
 $699万
 $18,538/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -41847,7 +41847,7 @@
           <t>E | 377呎 (1房)
 $702万
 $18,626/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -41855,7 +41855,7 @@
           <t>F | 525呎 (2房)
 $1009万
 $19,227/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41870,7 +41870,7 @@
           <t>A | 757呎 (3房)
 $1535万
 $20,277/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -41878,7 +41878,7 @@
           <t>B | 520呎 (2房)
 $1097万
 $21,088/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -41886,7 +41886,7 @@
           <t>C | 388呎 (1房)
 $691万
 $17,799/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -41894,7 +41894,7 @@
           <t>D | 377呎 (1房)
 $698万
 $18,501/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -41902,7 +41902,7 @@
           <t>E | 377呎 (1房)
 $701万
 $18,589/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -41910,7 +41910,7 @@
           <t>F | 525呎 (2房)
 $1004万
 $19,131/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41925,7 +41925,7 @@
           <t>A | 757呎 (3房)
 $1565万
 $20,670/呎
-(24年-05月-13日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -41933,7 +41933,7 @@
           <t>B | 520呎 (2房)
 $1065万
 $20,485/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -41941,7 +41941,7 @@
           <t>C | 388呎 (1房)
 $706万
 $18,183/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -41949,7 +41949,7 @@
           <t>D | 377呎 (1房)
 $696万
 $18,464/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -41957,7 +41957,7 @@
           <t>E | 377呎 (1房)
 $699万
 $18,552/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -41965,7 +41965,7 @@
           <t>F | 525呎 (2房)
 $1024万
 $19,501/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -41980,7 +41980,7 @@
           <t>A | 716呎 (3房)
 $1627万
 $22,722/呎
-(24年-05月-13日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -41988,7 +41988,7 @@
           <t>B | 480呎 (2房)
 $1107万
 $23,058/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -41996,7 +41996,7 @@
           <t>C | 350呎 (1房)
 $736万
 $21,029/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -42004,7 +42004,7 @@
           <t>D | 340呎 (1房)
 $742万
 $21,812/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -42012,7 +42012,7 @@
           <t>E | 340呎 (1房)
 $746万
 $21,935/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -42020,7 +42020,7 @@
           <t>F | 487呎 (2房)
 $1080万
 $22,181/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-朗贤峰第IIB期.xlsx
+++ b/files/九龙-何文田-朗贤峰第IIB期.xlsx
@@ -36387,7 +36387,7 @@
           <t>C | 390呎 (1房)
 $880万
 $22,559/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -36395,7 +36395,7 @@
           <t>D | 539呎 (2房)
 $1467万
 $27,219/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -36403,7 +36403,7 @@
           <t>E | 488呎 (2房)
 $1333万
 $27,316/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -36426,7 +36426,7 @@
           <t>A | 783呎 (3房)
 $2031万
 $25,935/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -36434,7 +36434,7 @@
           <t>B | 536呎 (2房)
 $1336万
 $24,924/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -36442,7 +36442,7 @@
           <t>C | 388呎 (1房)
 $836万
 $21,549/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -36450,7 +36450,7 @@
           <t>D | 539呎 (2房)
 $1338万
 $24,827/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -36458,7 +36458,7 @@
           <t>E | 488呎 (2房)
 $1216万
 $24,922/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -36466,7 +36466,7 @@
           <t>F | 555呎 (2房)
 $1447万
 $26,077/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -36481,7 +36481,7 @@
           <t>A | 783呎 (3房)
 $2021万
 $25,808/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -36497,7 +36497,7 @@
           <t>C | 388呎 (1房)
 $815万
 $20,995/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -36505,7 +36505,7 @@
           <t>D | 539呎 (2房)
 $1325万
 $24,584/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -36513,7 +36513,7 @@
           <t>E | 488呎 (2房)
 $1263万
 $25,883/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -36536,7 +36536,7 @@
           <t>A | 783呎 (3房)
 $1992万
 $25,434/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -36544,7 +36544,7 @@
           <t>B | 536呎 (2房)
 $1310万
 $24,438/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -36552,7 +36552,7 @@
           <t>C | 388呎 (1房)
 $805万
 $20,747/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -36560,7 +36560,7 @@
           <t>D | 539呎 (2房)
 $1300万
 $24,109/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -36568,7 +36568,7 @@
           <t>E | 488呎 (2房)
 $1210万
 $24,791/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -36576,7 +36576,7 @@
           <t>F | 555呎 (2房)
 $1440万
 $25,941/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -36591,7 +36591,7 @@
           <t>A | 783呎 (3房)
 $1982万
 $25,310/呎
-(24年-10月)</t>
+(24年-10月-08日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -36607,7 +36607,7 @@
           <t>C | 388呎 (1房)
 $803万
 $20,706/呎
-(24年-07月)</t>
+(24年-07月-01日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -36615,7 +36615,7 @@
           <t>D | 539呎 (2房)
 $1287万
 $23,874/呎
-(24年-07月)</t>
+(24年-07月-24日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -36623,7 +36623,7 @@
           <t>E | 488呎 (2房)
 $1170万
 $23,965/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -36631,7 +36631,7 @@
           <t>F | 555呎 (2房)
 $1426万
 $25,686/呎
-(24年-07月)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
     </row>
@@ -36646,7 +36646,7 @@
           <t>A | 783呎 (3房)
 $1972万
 $25,186/呎
-(24年-07月)</t>
+(24年-07月-16日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -36662,7 +36662,7 @@
           <t>C | 388呎 (1房)
 $802万
 $20,665/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -36670,7 +36670,7 @@
           <t>D | 539呎 (2房)
 $1274万
 $23,640/呎
-(24年-07月)</t>
+(24年-07月-17日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -36678,7 +36678,7 @@
           <t>E | 488呎 (2房)
 $1158万
 $23,732/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -36686,7 +36686,7 @@
           <t>F | 555呎 (2房)
 $1365万
 $24,589/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
     </row>
@@ -36701,7 +36701,7 @@
           <t>A | 783呎 (3房)
 $2010万
 $25,676/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -36717,7 +36717,7 @@
           <t>C | 388呎 (1房)
 $800万
 $20,624/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -36725,7 +36725,7 @@
           <t>D | 539呎 (2房)
 $1262万
 $23,410/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -36733,7 +36733,7 @@
           <t>E | 488呎 (2房)
 $1147万
 $23,500/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -36741,7 +36741,7 @@
           <t>F | 555呎 (2房)
 $1371万
 $24,703/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -36756,7 +36756,7 @@
           <t>A | 783呎 (3房)
 $1953万
 $24,941/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -36764,7 +36764,7 @@
           <t>B | 536呎 (2房)
 $1316万
 $24,547/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -36772,7 +36772,7 @@
           <t>C | 388呎 (1房)
 $799万
 $20,582/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -36780,7 +36780,7 @@
           <t>D | 539呎 (2房)
 $1280万
 $23,746/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -36788,7 +36788,7 @@
           <t>E | 488呎 (2房)
 $1163万
 $23,838/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -36796,7 +36796,7 @@
           <t>F | 555呎 (2房)
 $1344万
 $24,223/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -36811,7 +36811,7 @@
           <t>A | 783呎 (3房)
 $1991万
 $25,425/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -36819,7 +36819,7 @@
           <t>B | 536呎 (2房)
 $1278万
 $23,845/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -36827,7 +36827,7 @@
           <t>C | 388呎 (1房)
 $817万
 $21,046/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -36835,7 +36835,7 @@
           <t>D | 539呎 (2房)
 $1237万
 $22,954/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -36843,7 +36843,7 @@
           <t>E | 488呎 (2房)
 $1152万
 $23,609/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -36851,7 +36851,7 @@
           <t>F | 555呎 (2房)
 $1318万
 $23,755/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -36866,7 +36866,7 @@
           <t>A | 783呎 (3房)
 $1943万
 $24,820/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -36874,7 +36874,7 @@
           <t>B | 536呎 (2房)
 $1278万
 $23,845/呎
-(24年-06月)</t>
+(24年-06月-23日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -36882,7 +36882,7 @@
           <t>C | 388呎 (1房)
 $797万
 $20,544/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -36890,7 +36890,7 @@
           <t>D | 539呎 (2房)
 $1237万
 $22,954/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -36898,7 +36898,7 @@
           <t>E | 488呎 (2房)
 $1125万
 $23,045/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -36906,7 +36906,7 @@
           <t>F | 555呎 (2房)
 $1306万
 $23,524/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -36921,7 +36921,7 @@
           <t>A | 783呎 (3房)
 $1924万
 $24,579/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -36929,7 +36929,7 @@
           <t>B | 536呎 (2房)
 $1266万
 $23,612/呎
-(24年-06月)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -36937,7 +36937,7 @@
           <t>C | 388呎 (1房)
 $792万
 $20,399/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -36945,7 +36945,7 @@
           <t>D | 539呎 (2房)
 $1255万
 $23,284/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -36953,7 +36953,7 @@
           <t>E | 488呎 (2房)
 $1141万
 $23,375/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -36961,7 +36961,7 @@
           <t>F | 555呎 (2房)
 $1238万
 $22,305/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -36976,7 +36976,7 @@
           <t>A | 783呎 (3房)
 $1962万
 $25,055/呎
-(24年-06月)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -36992,7 +36992,7 @@
           <t>C | 388呎 (1房)
 $790万
 $20,361/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -37000,7 +37000,7 @@
           <t>D | 539呎 (2房)
 $1219万
 $22,620/呎
-(24年-06月)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -37008,7 +37008,7 @@
           <t>E | 488呎 (2房)
 $1115万
 $22,848/呎
-(24年-10月)</t>
+(24年-10月-17日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -37016,7 +37016,7 @@
           <t>F | 555呎 (2房)
 $1244万
 $22,405/呎
-(24年-06月)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -37031,7 +37031,7 @@
           <t>A | 783呎 (3房)
 $1906万
 $24,340/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -37047,7 +37047,7 @@
           <t>C | 388呎 (1房)
 $808万
 $20,817/呎
-(24年-07月)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -37055,7 +37055,7 @@
           <t>D | 539呎 (2房)
 $1272万
 $23,607/呎
-(24年-06月)</t>
+(24年-06月-24日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -37063,7 +37063,7 @@
           <t>E | 488呎 (2房)
 $1103万
 $22,596/呎
-(24年-06月)</t>
+(24年-06月-24日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -37071,7 +37071,7 @@
           <t>F | 555呎 (2房)
 $1211万
 $21,825/呎
-(24年-07月)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
     </row>
@@ -37086,7 +37086,7 @@
           <t>A | 783呎 (3房)
 $1896万
 $24,221/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -37102,7 +37102,7 @@
           <t>C | 388呎 (1房)
 $806万
 $20,773/呎
-(24年-07月)</t>
+(24年-07月-01日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -37110,7 +37110,7 @@
           <t>D | 539呎 (2房)
 $1207万
 $22,397/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -37118,7 +37118,7 @@
           <t>E | 488呎 (2房)
 $1124万
 $23,035/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -37126,7 +37126,7 @@
           <t>F | 555呎 (2房)
 $1205万
 $21,717/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
     </row>
@@ -37141,7 +37141,7 @@
           <t>A | 783呎 (3房)
 $1869万
 $23,870/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -37157,7 +37157,7 @@
           <t>C | 388呎 (1房)
 $778万
 $20,041/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -37165,7 +37165,7 @@
           <t>D | 539呎 (2房)
 $1231万
 $22,831/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -37173,7 +37173,7 @@
           <t>E | 488呎 (2房)
 $1119万
 $22,922/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -37181,7 +37181,7 @@
           <t>F | 555呎 (2房)
 $1171万
 $21,095/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -37196,7 +37196,7 @@
           <t>A | 783呎 (3房)
 $1887万
 $24,098/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -37212,7 +37212,7 @@
           <t>C | 388呎 (1房)
 $787万
 $20,289/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -37220,7 +37220,7 @@
           <t>D | 539呎 (2房)
 $1225万
 $22,720/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -37228,7 +37228,7 @@
           <t>E | 488呎 (2房)
 $1087万
 $22,266/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -37236,7 +37236,7 @@
           <t>F | 555呎 (2房)
 $1165万
 $20,993/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -37251,7 +37251,7 @@
           <t>A | 783呎 (3房)
 $1860万
 $23,750/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -37267,7 +37267,7 @@
           <t>C | 388呎 (1房)
 $759万
 $19,570/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -37275,7 +37275,7 @@
           <t>D | 539呎 (2房)
 $1219万
 $22,609/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -37283,7 +37283,7 @@
           <t>E | 488呎 (2房)
 $1108万
 $22,699/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -37291,7 +37291,7 @@
           <t>F | 555呎 (2房)
 $1188万
 $21,400/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -37306,7 +37306,7 @@
           <t>A | 783呎 (3房)
 $1798万
 $22,959/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -37314,7 +37314,7 @@
           <t>B | 536呎 (2房)
 $1210万
 $22,584/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -37322,7 +37322,7 @@
           <t>C | 388呎 (1房)
 $752万
 $19,379/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -37330,7 +37330,7 @@
           <t>D | 539呎 (2房)
 $1219万
 $22,609/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -37338,7 +37338,7 @@
           <t>E | 488呎 (2房)
 $1108万
 $22,699/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -37346,7 +37346,7 @@
           <t>F | 555呎 (2房)
 $1188万
 $21,400/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -37361,7 +37361,7 @@
           <t>A | 783呎 (3房)
 $1806万
 $23,068/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -37377,7 +37377,7 @@
           <t>C | 388呎 (1房)
 $757万
 $19,521/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -37385,7 +37385,7 @@
           <t>D | 539呎 (2房)
 $1178万
 $21,855/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -37393,7 +37393,7 @@
           <t>E | 488呎 (2房)
 $1097万
 $22,480/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -37401,7 +37401,7 @@
           <t>F | 555呎 (2房)
 $1148万
 $20,686/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -37416,7 +37416,7 @@
           <t>A | 783呎 (3房)
 $1797万
 $22,955/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -37432,7 +37432,7 @@
           <t>C | 388呎 (1房)
 $756万
 $19,482/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -37440,7 +37440,7 @@
           <t>D | 539呎 (2房)
 $1201万
 $22,278/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -37448,7 +37448,7 @@
           <t>E | 488呎 (2房)
 $1066万
 $21,834/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -37456,7 +37456,7 @@
           <t>F | 555呎 (2房)
 $1142万
 $20,584/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -37471,7 +37471,7 @@
           <t>A | 783呎 (3房)
 $1789万
 $22,844/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -37487,7 +37487,7 @@
           <t>C | 388呎 (1房)
 $754万
 $19,446/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -37495,7 +37495,7 @@
           <t>D | 539呎 (2房)
 $1166万
 $21,640/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -37503,7 +37503,7 @@
           <t>E | 488呎 (2房)
 $1060万
 $21,727/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -37511,7 +37511,7 @@
           <t>F | 555呎 (2房)
 $1137万
 $20,483/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -37542,7 +37542,7 @@
           <t>C | 388呎 (1房)
 $735万
 $18,943/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -37550,7 +37550,7 @@
           <t>D | 539呎 (2房)
 $1189万
 $22,059/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -37558,7 +37558,7 @@
           <t>E | 488呎 (2房)
 $1055万
 $21,621/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -37566,7 +37566,7 @@
           <t>F | 555呎 (2房)
 $1131万
 $20,384/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -37597,7 +37597,7 @@
           <t>C | 388呎 (1房)
 $734万
 $18,905/呎
-(24年-06月)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -37605,7 +37605,7 @@
           <t>D | 539呎 (2房)
 $1155万
 $21,429/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -37613,7 +37613,7 @@
           <t>E | 488呎 (2房)
 $1050万
 $21,516/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -37621,7 +37621,7 @@
           <t>F | 555呎 (2房)
 $1126万
 $20,283/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
     </row>
@@ -37636,7 +37636,7 @@
           <t>A | 740呎 (3房)
 $1934万
 $26,134/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -37644,7 +37644,7 @@
           <t>B | 498呎 (2房)
 $1219万
 $24,474/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -37660,7 +37660,7 @@
           <t>D | 502呎 (2房)
 $1231万
 $24,518/呎
-(24年-06月)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -37668,7 +37668,7 @@
           <t>E | 450呎 (2房)
 $1120万
 $24,889/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -37676,7 +37676,7 @@
           <t>F | 517呎 (2房)
 $1171万
 $22,646/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -37835,7 +37835,7 @@
           <t>C | 387呎 (1房)
 $856万
 $22,106/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -37843,7 +37843,7 @@
           <t>D | 377呎 (1房)
 $858万
 $22,772/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -37851,7 +37851,7 @@
           <t>E | 377呎 (1房)
 $836万
 $22,175/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -37859,7 +37859,7 @@
           <t>F | 525呎 (2房)
 $1402万
 $26,709/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -37874,7 +37874,7 @@
           <t>A | 757呎 (3房)
 $1970万
 $26,026/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -37890,7 +37890,7 @@
           <t>C | 387呎 (1房)
 $799万
 $20,651/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -37898,7 +37898,7 @@
           <t>D | 377呎 (1房)
 $801万
 $21,249/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -37906,7 +37906,7 @@
           <t>E | 378呎 (1房)
 $780万
 $20,638/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -37914,7 +37914,7 @@
           <t>F | 525呎 (2房)
 $1244万
 $23,688/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -37929,7 +37929,7 @@
           <t>A | 757呎 (3房)
 $2046万
 $27,032/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -37937,7 +37937,7 @@
           <t>B | 521呎 (2房)
 $1354万
 $25,983/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -37945,7 +37945,7 @@
           <t>C | 387呎 (1房)
 $798万
 $20,610/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -37953,7 +37953,7 @@
           <t>D | 377呎 (1房)
 $800万
 $21,207/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -37961,7 +37961,7 @@
           <t>E | 377呎 (1房)
 $779万
 $20,653/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -37969,7 +37969,7 @@
           <t>F | 525呎 (2房)
 $1268万
 $24,145/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -37984,7 +37984,7 @@
           <t>A | 757呎 (3房)
 $1960万
 $25,896/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -37992,7 +37992,7 @@
           <t>B | 521呎 (2房)
 $1296万
 $24,871/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -38000,7 +38000,7 @@
           <t>C | 387呎 (1房)
 $807万
 $20,863/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -38008,7 +38008,7 @@
           <t>D | 377呎 (1房)
 $790万
 $20,958/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -38016,7 +38016,7 @@
           <t>E | 377呎 (1房)
 $788万
 $20,907/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -38024,7 +38024,7 @@
           <t>F | 525呎 (2房)
 $1219万
 $23,223/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -38039,7 +38039,7 @@
           <t>A | 757呎 (3房)
 $1895万
 $25,033/呎
-(24年-06月)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -38047,7 +38047,7 @@
           <t>B | 521呎 (2房)
 $1283万
 $24,628/呎
-(24年-09月)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -38055,7 +38055,7 @@
           <t>C | 387呎 (1房)
 $787万
 $20,326/呎
-(24年-06月)</t>
+(24年-06月-24日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -38063,7 +38063,7 @@
           <t>D | 377呎 (1房)
 $770万
 $20,416/呎
-(24年-06月)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -38071,7 +38071,7 @@
           <t>E | 377呎 (1房)
 $768万
 $20,369/呎
-(24年-06月)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -38079,7 +38079,7 @@
           <t>F | 525呎 (2房)
 $1213万
 $23,109/呎
-(24年-06月)</t>
+(24年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -38094,7 +38094,7 @@
           <t>A | 757呎 (3房)
 $1922万
 $25,394/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -38102,7 +38102,7 @@
           <t>B | 521呎 (2房)
 $1271万
 $24,388/呎
-(24年-09月)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -38110,7 +38110,7 @@
           <t>C | 387呎 (1房)
 $804万
 $20,780/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -38118,7 +38118,7 @@
           <t>D | 377呎 (1房)
 $768万
 $20,377/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -38126,7 +38126,7 @@
           <t>E | 377呎 (1房)
 $766万
 $20,329/呎
-(24年-07月)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -38134,7 +38134,7 @@
           <t>F | 525呎 (2房)
 $1207万
 $22,992/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
     </row>
@@ -38149,7 +38149,7 @@
           <t>A | 757呎 (3房)
 $1904万
 $25,148/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -38157,7 +38157,7 @@
           <t>B | 521呎 (2房)
 $1258万
 $24,150/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -38165,7 +38165,7 @@
           <t>C | 387呎 (1房)
 $784万
 $20,245/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -38173,7 +38173,7 @@
           <t>D | 377呎 (1房)
 $785万
 $20,833/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -38181,7 +38181,7 @@
           <t>E | 377呎 (1房)
 $765万
 $20,289/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -38189,7 +38189,7 @@
           <t>F | 525呎 (2房)
 $1206万
 $22,981/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -38204,7 +38204,7 @@
           <t>A | 757呎 (3房)
 $1840万
 $24,312/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -38212,7 +38212,7 @@
           <t>B | 521呎 (2房)
 $1276万
 $24,497/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -38220,7 +38220,7 @@
           <t>C | 387呎 (1房)
 $801万
 $20,700/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -38228,7 +38228,7 @@
           <t>D | 377呎 (1房)
 $803万
 $21,289/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -38236,7 +38236,7 @@
           <t>E | 377呎 (1房)
 $763万
 $20,247/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -38244,7 +38244,7 @@
           <t>F | 525呎 (2房)
 $1172万
 $22,324/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -38259,7 +38259,7 @@
           <t>A | 757呎 (3房)
 $1867万
 $24,663/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -38267,7 +38267,7 @@
           <t>B | 521呎 (2房)
 $1234万
 $23,681/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -38275,7 +38275,7 @@
           <t>C | 387呎 (1房)
 $780万
 $20,165/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -38283,7 +38283,7 @@
           <t>D | 377呎 (1房)
 $764万
 $20,255/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -38291,7 +38291,7 @@
           <t>E | 378呎 (1房)
 $780万
 $20,646/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -38299,7 +38299,7 @@
           <t>F | 525呎 (2房)
 $1195万
 $22,754/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -38314,7 +38314,7 @@
           <t>A | 757呎 (3房)
 $1822万
 $24,074/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -38322,7 +38322,7 @@
           <t>B | 521呎 (2房)
 $1234万
 $23,681/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -38330,7 +38330,7 @@
           <t>C | 387呎 (1房)
 $780万
 $20,165/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -38338,7 +38338,7 @@
           <t>D | 377呎 (1房)
 $782万
 $20,748/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -38346,7 +38346,7 @@
           <t>E | 377呎 (1房)
 $799万
 $21,191/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -38354,7 +38354,7 @@
           <t>F | 524呎 (2房)
 $1195万
 $22,798/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -38369,7 +38369,7 @@
           <t>A | 757呎 (3房)
 $1762万
 $23,273/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -38377,7 +38377,7 @@
           <t>B | 521呎 (2房)
 $1252万
 $24,021/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -38385,7 +38385,7 @@
           <t>C | 387呎 (1房)
 $794万
 $20,514/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -38393,7 +38393,7 @@
           <t>D | 377呎 (1房)
 $777万
 $20,607/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -38401,7 +38401,7 @@
           <t>E | 378呎 (1房)
 $757万
 $20,016/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -38409,7 +38409,7 @@
           <t>F | 525呎 (2房)
 $1155万
 $21,994/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -38424,7 +38424,7 @@
           <t>A | 757呎 (3房)
 $1753万
 $23,160/呎
-(24年-07月)</t>
+(24年-07月-01日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -38432,7 +38432,7 @@
           <t>B | 521呎 (2房)
 $1216万
 $23,334/呎
-(24年-06月)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -38440,7 +38440,7 @@
           <t>C | 388呎 (1房)
 $774万
 $19,936/呎
-(24年-07月)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -38448,7 +38448,7 @@
           <t>D | 377呎 (1房)
 $757万
 $20,077/呎
-(24年-07月)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -38456,7 +38456,7 @@
           <t>E | 377呎 (1房)
 $755万
 $20,029/呎
-(24年-07月)</t>
+(24年-07月-01日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -38464,7 +38464,7 @@
           <t>F | 525呎 (2房)
 $1149万
 $21,884/呎
-(24年-07月)</t>
+(24年-07月-01日)</t>
         </is>
       </c>
     </row>
@@ -38479,7 +38479,7 @@
           <t>A | 757呎 (3房)
 $1745万
 $23,048/呎
-(24年-06月)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -38487,7 +38487,7 @@
           <t>B | 521呎 (2房)
 $1210万
 $23,221/呎
-(24年-06月)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -38495,7 +38495,7 @@
           <t>C | 387呎 (1房)
 $772万
 $19,946/呎
-(24年-06月)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -38503,7 +38503,7 @@
           <t>D | 377呎 (1房)
 $774万
 $20,525/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -38511,7 +38511,7 @@
           <t>E | 377呎 (1房)
 $754万
 $19,989/呎
-(24年-06月)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -38519,7 +38519,7 @@
           <t>F | 525呎 (2房)
 $1143万
 $21,777/呎
-(24年-06月)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -38534,7 +38534,7 @@
           <t>A | 757呎 (3房)
 $1736万
 $22,935/呎
-(24年-07月)</t>
+(24年-07月-01日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -38542,7 +38542,7 @@
           <t>B | 521呎 (2房)
 $1233万
 $23,668/呎
-(24年-07月)</t>
+(24年-07月-10日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -38550,7 +38550,7 @@
           <t>C | 387呎 (1房)
 $789万
 $20,393/呎
-(24年-07月)</t>
+(24年-07月-01日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -38558,7 +38558,7 @@
           <t>D | 377呎 (1房)
 $754万
 $19,997/呎
-(24年-08月)</t>
+(24年-08月-18日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -38566,7 +38566,7 @@
           <t>E | 377呎 (1房)
 $752万
 $19,950/呎
-(24年-07月)</t>
+(24年-07月-24日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -38574,7 +38574,7 @@
           <t>F | 525呎 (2房)
 $1138万
 $21,669/呎
-(24年-07月)</t>
+(24年-07月-01日)</t>
         </is>
       </c>
     </row>
@@ -38589,7 +38589,7 @@
           <t>A | 757呎 (3房)
 $1728万
 $22,823/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -38597,7 +38597,7 @@
           <t>B | 521呎 (2房)
 $1227万
 $23,555/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -38605,7 +38605,7 @@
           <t>C | 387呎 (1房)
 $761万
 $19,672/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -38613,7 +38613,7 @@
           <t>D | 377呎 (1房)
 $763万
 $20,241/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -38621,7 +38621,7 @@
           <t>E | 377呎 (1房)
 $761万
 $20,194/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -38629,7 +38629,7 @@
           <t>F | 525呎 (2房)
 $1121万
 $21,349/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -38644,7 +38644,7 @@
           <t>A | 757呎 (3房)
 $1761万
 $23,266/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -38652,7 +38652,7 @@
           <t>B | 521呎 (2房)
 $1221万
 $23,440/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -38660,7 +38660,7 @@
           <t>C | 387呎 (1房)
 $752万
 $19,442/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -38668,7 +38668,7 @@
           <t>D | 377呎 (1房)
 $736万
 $19,528/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -38676,7 +38676,7 @@
           <t>E | 377呎 (1房)
 $752万
 $19,955/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -38684,7 +38684,7 @@
           <t>F | 525呎 (2房)
 $1104万
 $21,034/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -38699,7 +38699,7 @@
           <t>A | 757呎 (3房)
 $1711万
 $22,601/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -38707,7 +38707,7 @@
           <t>B | 521呎 (2房)
 $1186万
 $22,768/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -38715,7 +38715,7 @@
           <t>C | 387呎 (1房)
 $762万
 $19,680/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -38723,7 +38723,7 @@
           <t>D | 377呎 (1房)
 $728万
 $19,297/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -38731,7 +38731,7 @@
           <t>E | 377呎 (1房)
 $726万
 $19,252/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -38739,7 +38739,7 @@
           <t>F | 525呎 (2房)
 $1088万
 $20,726/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -38754,7 +38754,7 @@
           <t>A | 757呎 (3房)
 $1711万
 $22,601/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -38762,7 +38762,7 @@
           <t>B | 521呎 (2房)
 $1186万
 $22,768/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -38770,7 +38770,7 @@
           <t>C | 388呎 (1房)
 $736万
 $18,974/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -38778,7 +38778,7 @@
           <t>D | 378呎 (1房)
 $738万
 $19,521/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -38786,7 +38786,7 @@
           <t>E | 377呎 (1房)
 $754万
 $19,989/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -38794,7 +38794,7 @@
           <t>F | 524呎 (2房)
 $1104万
 $21,063/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -38809,7 +38809,7 @@
           <t>A | 757呎 (3房)
 $1694万
 $22,383/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -38817,7 +38817,7 @@
           <t>B | 521呎 (2房)
 $1175万
 $22,545/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -38825,7 +38825,7 @@
           <t>C | 387呎 (1房)
 $724万
 $18,705/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -38833,7 +38833,7 @@
           <t>D | 377呎 (1房)
 $726万
 $19,249/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -38841,7 +38841,7 @@
           <t>E | 377呎 (1房)
 $724万
 $19,202/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -38849,7 +38849,7 @@
           <t>F | 525呎 (2房)
 $1056万
 $20,120/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
     </row>
@@ -38864,7 +38864,7 @@
           <t>A | 757呎 (3房)
 $1686万
 $22,273/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -38872,7 +38872,7 @@
           <t>B | 521呎 (2房)
 $1169万
 $22,436/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -38880,7 +38880,7 @@
           <t>C | 387呎 (1房)
 $722万
 $18,669/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -38888,7 +38888,7 @@
           <t>D | 377呎 (1房)
 $724万
 $19,210/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -38896,7 +38896,7 @@
           <t>E | 377呎 (1房)
 $705万
 $18,708/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -38904,7 +38904,7 @@
           <t>F | 525呎 (2房)
 $1051万
 $20,021/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -38919,7 +38919,7 @@
           <t>A | 757呎 (3房)
 $1678万
 $22,165/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -38927,7 +38927,7 @@
           <t>B | 521呎 (2房)
 $1192万
 $22,869/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -38935,7 +38935,7 @@
           <t>C | 387呎 (1房)
 $739万
 $19,088/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -38943,7 +38943,7 @@
           <t>D | 377呎 (1房)
 $706万
 $18,716/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -38951,7 +38951,7 @@
           <t>E | 377呎 (1房)
 $704万
 $18,671/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -38959,7 +38959,7 @@
           <t>F | 525呎 (2房)
 $1071万
 $20,408/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -38974,7 +38974,7 @@
           <t>A | 757呎 (3房)
 $1670万
 $22,058/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -38982,7 +38982,7 @@
           <t>B | 521呎 (2房)
 $1186万
 $22,758/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -38990,7 +38990,7 @@
           <t>C | 387呎 (1房)
 $737万
 $19,049/呎
-(24年-06月)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -38998,7 +38998,7 @@
           <t>D | 377呎 (1房)
 $704万
 $18,679/呎
-(24年-06月)</t>
+(24年-06月-06日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -39006,7 +39006,7 @@
           <t>E | 377呎 (1房)
 $702万
 $18,634/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -39014,7 +39014,7 @@
           <t>F | 525呎 (2房)
 $1041万
 $19,823/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -39029,7 +39029,7 @@
           <t>A | 757呎 (3房)
 $1702万
 $22,485/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -39037,7 +39037,7 @@
           <t>B | 521呎 (2房)
 $1152万
 $22,107/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -39045,7 +39045,7 @@
           <t>C | 387呎 (1房)
 $718万
 $18,558/呎
-(24年-06月)</t>
+(24年-06月-20日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -39053,7 +39053,7 @@
           <t>D | 377呎 (1房)
 $703万
 $18,642/呎
-(24年-06月)</t>
+(24年-06月-11日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -39061,7 +39061,7 @@
           <t>E | 377呎 (1房)
 $718万
 $19,050/呎
-(24年-06月)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -39069,7 +39069,7 @@
           <t>F | 525呎 (2房)
 $1036万
 $19,726/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -39084,7 +39084,7 @@
           <t>A | 716呎 (3房)
 $1769万
 $24,707/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -39092,7 +39092,7 @@
           <t>B | 481呎 (2房)
 $1196万
 $24,871/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -39100,7 +39100,7 @@
           <t>C | 350呎 (1房)
 $753万
 $21,509/呎
-(24年-06月)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -39108,7 +39108,7 @@
           <t>D | 340呎 (1房)
 $732万
 $21,532/呎
-(24年-06月)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -39116,7 +39116,7 @@
           <t>E | 340呎 (1房)
 $748万
 $22,003/呎
-(24年-05月)</t>
+(24年-05月-25日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -39124,7 +39124,7 @@
           <t>F | 487呎 (2房)
 $1140万
 $23,405/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -39282,7 +39282,7 @@
           <t>B | 761呎 (3房)
 $1960万
 $25,761/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -39290,7 +39290,7 @@
           <t>C | 497呎 (2房)
 $1289万
 $25,932/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -39298,7 +39298,7 @@
           <t>D | 388呎 (1房)
 $863万
 $22,250/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -39306,7 +39306,7 @@
           <t>E | 391呎 (1房)
 $858万
 $21,944/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr"/>
@@ -39322,7 +39322,7 @@
           <t>A | 774呎 (3房)
 $2051万
 $26,497/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -39330,7 +39330,7 @@
           <t>B | 760呎 (3房)
 $1859万
 $24,455/呎
-(24年-06月)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -39338,7 +39338,7 @@
           <t>C | 497呎 (2房)
 $1142万
 $22,978/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -39346,7 +39346,7 @@
           <t>D | 388呎 (1房)
 $789万
 $20,330/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -39354,7 +39354,7 @@
           <t>E | 388呎 (1房)
 $808万
 $20,812/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -39362,7 +39362,7 @@
           <t>F | 528呎 (2房)
 $1334万
 $25,263/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -39377,7 +39377,7 @@
           <t>A | 774呎 (3房)
 $2030万
 $26,234/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -39385,7 +39385,7 @@
           <t>B | 760呎 (3房)
 $1849万
 $24,334/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -39393,7 +39393,7 @@
           <t>C | 497呎 (2房)
 $1136万
 $22,865/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -39401,7 +39401,7 @@
           <t>D | 388呎 (1房)
 $787万
 $20,289/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -39409,7 +39409,7 @@
           <t>E | 388呎 (1房)
 $773万
 $19,925/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -39417,7 +39417,7 @@
           <t>F | 528呎 (2房)
 $1321万
 $25,013/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -39432,7 +39432,7 @@
           <t>A | 774呎 (3房)
 $1991万
 $25,720/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -39440,7 +39440,7 @@
           <t>B | 760呎 (3房)
 $1779万
 $23,408/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -39448,7 +39448,7 @@
           <t>C | 497呎 (2房)
 $1147万
 $23,082/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -39456,7 +39456,7 @@
           <t>D | 388呎 (1房)
 $797万
 $20,544/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -39464,7 +39464,7 @@
           <t>E | 388呎 (1房)
 $758万
 $19,526/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -39472,7 +39472,7 @@
           <t>F | 528呎 (2房)
 $1264万
 $23,939/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
     </row>
@@ -39487,7 +39487,7 @@
           <t>A | 774呎 (3房)
 $1924万
 $24,859/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -39495,7 +39495,7 @@
           <t>B | 760呎 (3房)
 $1813万
 $23,861/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -39503,7 +39503,7 @@
           <t>C | 497呎 (2房)
 $1142万
 $22,970/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -39511,7 +39511,7 @@
           <t>D | 388呎 (1房)
 $796万
 $20,503/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -39519,7 +39519,7 @@
           <t>E | 388呎 (1房)
 $745万
 $19,201/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -39527,7 +39527,7 @@
           <t>F | 528呎 (2房)
 $1252万
 $23,703/呎
-(24年-06月)</t>
+(24年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -39542,7 +39542,7 @@
           <t>A | 774呎 (3房)
 $1961万
 $25,339/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -39550,7 +39550,7 @@
           <t>B | 760呎 (3房)
 $1762万
 $23,178/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -39558,7 +39558,7 @@
           <t>C | 497呎 (2房)
 $1136万
 $22,855/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -39566,7 +39566,7 @@
           <t>D | 388呎 (1房)
 $794万
 $20,461/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -39574,7 +39574,7 @@
           <t>E | 389呎 (1房)
 $752万
 $19,332/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -39582,7 +39582,7 @@
           <t>F | 528呎 (2房)
 $1276万
 $24,161/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -39597,7 +39597,7 @@
           <t>A | 774呎 (3房)
 $1952万
 $25,213/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -39605,7 +39605,7 @@
           <t>B | 760呎 (3房)
 $1796万
 $23,626/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -39613,7 +39613,7 @@
           <t>C | 497呎 (2房)
 $1130万
 $22,744/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -39621,7 +39621,7 @@
           <t>D | 388呎 (1房)
 $792万
 $20,423/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -39629,7 +39629,7 @@
           <t>E | 388呎 (1房)
 $727万
 $18,727/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -39637,7 +39637,7 @@
           <t>F | 528呎 (2房)
 $1239万
 $23,468/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -39652,7 +39652,7 @@
           <t>A | 774呎 (3房)
 $1942万
 $25,087/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -39660,7 +39660,7 @@
           <t>B | 760呎 (3房)
 $1787万
 $23,511/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -39668,7 +39668,7 @@
           <t>C | 497呎 (2房)
 $1125万
 $22,632/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -39676,7 +39676,7 @@
           <t>D | 392呎 (1房)
 $772万
 $19,694/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -39684,7 +39684,7 @@
           <t>E | 388呎 (1房)
 $725万
 $18,691/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -39692,7 +39692,7 @@
           <t>F | 528呎 (2房)
 $1263万
 $23,919/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -39707,7 +39707,7 @@
           <t>A | 774呎 (3房)
 $1849万
 $23,893/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -39715,7 +39715,7 @@
           <t>B | 760呎 (3房)
 $1778万
 $23,393/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -39723,7 +39723,7 @@
           <t>C | 497呎 (2房)
 $1119万
 $22,523/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -39731,7 +39731,7 @@
           <t>D | 388呎 (1房)
 $789万
 $20,343/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -39739,7 +39739,7 @@
           <t>E | 388呎 (1房)
 $724万
 $18,652/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -39747,7 +39747,7 @@
           <t>F | 528呎 (2房)
 $1257万
 $23,801/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -39762,7 +39762,7 @@
           <t>A | 774呎 (3房)
 $1813万
 $23,424/呎
-(24年-05月)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -39770,7 +39770,7 @@
           <t>B | 760呎 (3房)
 $1736万
 $22,837/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -39778,7 +39778,7 @@
           <t>C | 497呎 (2房)
 $1093万
 $21,986/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -39786,7 +39786,7 @@
           <t>D | 388呎 (1房)
 $770万
 $19,858/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -39794,7 +39794,7 @@
           <t>E | 388呎 (1房)
 $724万
 $18,652/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -39802,7 +39802,7 @@
           <t>F | 528呎 (2房)
 $1232万
 $23,333/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -39817,7 +39817,7 @@
           <t>A | 774呎 (3房)
 $1760万
 $22,742/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -39825,7 +39825,7 @@
           <t>B | 760呎 (3房)
 $1719万
 $22,613/呎
-(24年-05月)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -39833,7 +39833,7 @@
           <t>C | 497呎 (2房)
 $1082万
 $21,773/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -39841,7 +39841,7 @@
           <t>D | 388呎 (1房)
 $784万
 $20,204/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -39849,7 +39849,7 @@
           <t>E | 389呎 (1房)
 $719万
 $18,476/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -39857,7 +39857,7 @@
           <t>F | 528呎 (2房)
 $1168万
 $22,116/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -39872,7 +39872,7 @@
           <t>A | 774呎 (3房)
 $1759万
 $22,729/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -39880,7 +39880,7 @@
           <t>B | 760呎 (3房)
 $1752万
 $23,050/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -39888,7 +39888,7 @@
           <t>C | 497呎 (2房)
 $1103万
 $22,195/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -39896,7 +39896,7 @@
           <t>D | 388呎 (1房)
 $782万
 $20,162/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -39904,7 +39904,7 @@
           <t>E | 388呎 (1房)
 $735万
 $18,938/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -39912,7 +39912,7 @@
           <t>F | 528呎 (2房)
 $1167万
 $22,102/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -39927,7 +39927,7 @@
           <t>A | 774呎 (3房)
 $1716万
 $22,174/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -39935,7 +39935,7 @@
           <t>B | 760呎 (3房)
 $1702万
 $22,391/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -39943,7 +39943,7 @@
           <t>C | 497呎 (2房)
 $1098万
 $22,085/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -39951,7 +39951,7 @@
           <t>D | 388呎 (1房)
 $781万
 $20,124/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -39959,7 +39959,7 @@
           <t>E | 388呎 (1房)
 $733万
 $18,897/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -39967,7 +39967,7 @@
           <t>F | 528呎 (2房)
 $1139万
 $21,564/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -39982,7 +39982,7 @@
           <t>A | 774呎 (3房)
 $1635万
 $21,119/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -39990,7 +39990,7 @@
           <t>B | 760呎 (3房)
 $1735万
 $22,824/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -39998,7 +39998,7 @@
           <t>C | 497呎 (2房)
 $1066万
 $21,455/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -40006,7 +40006,7 @@
           <t>D | 388呎 (1房)
 $779万
 $20,085/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -40014,7 +40014,7 @@
           <t>E | 388呎 (1房)
 $714万
 $18,412/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -40022,7 +40022,7 @@
           <t>F | 528呎 (2房)
 $1111万
 $21,036/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -40037,7 +40037,7 @@
           <t>A | 774呎 (3房)
 $1634万
 $21,106/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -40045,7 +40045,7 @@
           <t>B | 760呎 (3房)
 $1685万
 $22,171/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -40053,7 +40053,7 @@
           <t>C | 497呎 (2房)
 $1087万
 $21,869/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -40061,7 +40061,7 @@
           <t>D | 388呎 (1房)
 $778万
 $20,046/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -40069,7 +40069,7 @@
           <t>E | 388呎 (1房)
 $730万
 $18,825/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -40077,7 +40077,7 @@
           <t>F | 528呎 (2房)
 $1058万
 $20,036/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -40092,7 +40092,7 @@
           <t>A | 774呎 (3房)
 $1593万
 $20,579/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -40100,7 +40100,7 @@
           <t>B | 760呎 (3房)
 $1677万
 $22,062/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -40108,7 +40108,7 @@
           <t>C | 497呎 (2房)
 $1056万
 $21,243/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -40116,7 +40116,7 @@
           <t>D | 388呎 (1房)
 $758万
 $19,531/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -40124,7 +40124,7 @@
           <t>E | 388呎 (1房)
 $712万
 $18,338/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -40132,7 +40132,7 @@
           <t>F | 528呎 (2房)
 $1061万
 $20,100/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -40147,7 +40147,7 @@
           <t>A | 774呎 (3房)
 $1547万
 $19,988/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -40155,7 +40155,7 @@
           <t>B | 760呎 (3房)
 $1709万
 $22,488/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -40163,7 +40163,7 @@
           <t>C | 497呎 (2房)
 $1051万
 $21,141/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -40171,7 +40171,7 @@
           <t>D | 388呎 (1房)
 $756万
 $19,492/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -40179,7 +40179,7 @@
           <t>E | 388呎 (1房)
 $710万
 $18,302/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -40187,7 +40187,7 @@
           <t>F | 528呎 (2房)
 $1031万
 $19,525/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -40202,7 +40202,7 @@
           <t>A | 774呎 (3房)
 $1547万
 $19,988/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -40210,7 +40210,7 @@
           <t>B | 760呎 (3房)
 $1668万
 $21,953/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -40218,7 +40218,7 @@
           <t>C | 497呎 (2房)
 $1051万
 $21,141/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -40226,7 +40226,7 @@
           <t>D | 388呎 (1房)
 $756万
 $19,492/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -40234,7 +40234,7 @@
           <t>E | 388呎 (1房)
 $710万
 $18,302/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -40242,7 +40242,7 @@
           <t>F | 528呎 (2房)
 $1056万
 $20,000/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -40257,7 +40257,7 @@
           <t>A | 774呎 (3房)
 $1569万
 $20,273/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -40265,7 +40265,7 @@
           <t>B | 760呎 (3房)
 $1692万
 $22,268/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -40273,7 +40273,7 @@
           <t>C | 497呎 (2房)
 $1066万
 $21,447/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -40281,7 +40281,7 @@
           <t>D | 388呎 (1房)
 $769万
 $19,830/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -40289,7 +40289,7 @@
           <t>E | 388呎 (1房)
 $705万
 $18,175/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -40297,7 +40297,7 @@
           <t>F | 528呎 (2房)
 $1046万
 $19,803/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -40312,7 +40312,7 @@
           <t>A | 774呎 (3房)
 $1561万
 $20,173/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -40320,7 +40320,7 @@
           <t>B | 760呎 (3房)
 $1684万
 $22,159/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -40328,7 +40328,7 @@
           <t>C | 497呎 (2房)
 $1042万
 $20,960/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -40336,7 +40336,7 @@
           <t>D | 388呎 (1房)
 $750万
 $19,322/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -40344,7 +40344,7 @@
           <t>E | 388呎 (1房)
 $704万
 $18,139/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -40352,7 +40352,7 @@
           <t>F | 528呎 (2房)
 $1040万
 $19,706/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -40367,7 +40367,7 @@
           <t>A | 774呎 (3房)
 $1517万
 $19,594/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -40375,7 +40375,7 @@
           <t>B | 760呎 (3房)
 $1636万
 $21,525/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -40383,7 +40383,7 @@
           <t>C | 497呎 (2房)
 $1030万
 $20,730/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -40391,7 +40391,7 @@
           <t>D | 388呎 (1房)
 $748万
 $19,284/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -40399,7 +40399,7 @@
           <t>E | 388呎 (1房)
 $720万
 $18,544/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -40407,7 +40407,7 @@
           <t>F | 528呎 (2房)
 $1011万
 $19,140/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -40422,7 +40422,7 @@
           <t>A | 774呎 (3房)
 $1509万
 $19,497/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -40430,7 +40430,7 @@
           <t>B | 760呎 (3房)
 $1628万
 $21,418/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -40438,7 +40438,7 @@
           <t>C | 497呎 (2房)
 $1025万
 $20,630/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -40446,7 +40446,7 @@
           <t>D | 388呎 (1房)
 $747万
 $19,245/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -40454,7 +40454,7 @@
           <t>E | 388呎 (1房)
 $718万
 $18,508/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -40462,7 +40462,7 @@
           <t>F | 528呎 (2房)
 $1030万
 $19,509/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -40477,7 +40477,7 @@
           <t>A | 774呎 (3房)
 $1502万
 $19,401/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -40485,7 +40485,7 @@
           <t>B | 760呎 (3房)
 $1630万
 $21,443/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -40493,7 +40493,7 @@
           <t>C | 497呎 (2房)
 $1045万
 $21,030/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -40501,7 +40501,7 @@
           <t>D | 388呎 (1房)
 $764万
 $19,678/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -40509,7 +40509,7 @@
           <t>E | 388呎 (1房)
 $700万
 $18,031/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -40517,7 +40517,7 @@
           <t>F | 528呎 (2房)
 $1025万
 $19,413/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -40532,7 +40532,7 @@
           <t>A | 732呎 (3房)
 $1570万
 $21,455/呎
-(24年-05月)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -40540,7 +40540,7 @@
           <t>B | 719呎 (3房)
 $1742万
 $24,224/呎
-(24年-05月)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -40548,7 +40548,7 @@
           <t>C | 459呎 (2房)
 $1062万
 $23,126/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -40556,7 +40556,7 @@
           <t>D | 350呎 (1房)
 $793万
 $22,651/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -40564,7 +40564,7 @@
           <t>E | 350呎 (1房)
 $756万
 $21,589/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -40572,7 +40572,7 @@
           <t>F | 490呎 (2房)
 $1068万
 $21,788/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -40731,7 +40731,7 @@
           <t>C | 388呎 (1房)
 $812万
 $20,938/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -40739,7 +40739,7 @@
           <t>D | 377呎 (1房)
 $810万
 $21,475/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -40747,7 +40747,7 @@
           <t>E | 377呎 (1房)
 $794万
 $21,064/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -40755,7 +40755,7 @@
           <t>F | 525呎 (2房)
 $1259万
 $23,983/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -40770,7 +40770,7 @@
           <t>A | 757呎 (3房)
 $1818万
 $24,011/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -40778,7 +40778,7 @@
           <t>B | 520呎 (2房)
 $1267万
 $24,363/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -40786,7 +40786,7 @@
           <t>C | 388呎 (1房)
 $776万
 $20,005/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -40794,7 +40794,7 @@
           <t>D | 377呎 (1房)
 $737万
 $19,557/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -40802,7 +40802,7 @@
           <t>E | 377呎 (1房)
 $759万
 $20,130/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -40810,7 +40810,7 @@
           <t>F | 525呎 (2房)
 $1143万
 $21,771/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -40825,7 +40825,7 @@
           <t>A | 757呎 (3房)
 $1844万
 $24,354/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -40833,7 +40833,7 @@
           <t>B | 520呎 (2房)
 $1254万
 $24,123/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -40841,7 +40841,7 @@
           <t>C | 388呎 (1房)
 $765万
 $19,716/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -40849,7 +40849,7 @@
           <t>D | 377呎 (1房)
 $736万
 $19,517/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -40857,7 +40857,7 @@
           <t>E | 377呎 (1房)
 $757万
 $20,090/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -40865,7 +40865,7 @@
           <t>F | 525呎 (2房)
 $1165万
 $22,192/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -40880,7 +40880,7 @@
           <t>A | 757呎 (3房)
 $1807万
 $23,876/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -40888,7 +40888,7 @@
           <t>B | 520呎 (2房)
 $1230万
 $23,648/呎
-(24年-05月)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -40896,7 +40896,7 @@
           <t>C | 388呎 (1房)
 $736万
 $18,961/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -40904,7 +40904,7 @@
           <t>D | 377呎 (1房)
 $727万
 $19,286/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -40912,7 +40912,7 @@
           <t>E | 377呎 (1房)
 $748万
 $19,851/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -40920,7 +40920,7 @@
           <t>F | 525呎 (2房)
 $1120万
 $21,343/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -40935,7 +40935,7 @@
           <t>A | 757呎 (3房)
 $1747万
 $23,077/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -40943,7 +40943,7 @@
           <t>B | 520呎 (2房)
 $1218万
 $23,415/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -40951,7 +40951,7 @@
           <t>C | 388呎 (1房)
 $725万
 $18,680/呎
-(24年-05月)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -40959,7 +40959,7 @@
           <t>D | 377呎 (1房)
 $726万
 $19,249/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -40967,7 +40967,7 @@
           <t>E | 377呎 (1房)
 $729万
 $19,342/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -40975,7 +40975,7 @@
           <t>F | 525呎 (2房)
 $1142万
 $21,754/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -40990,7 +40990,7 @@
           <t>A | 757呎 (3房)
 $1730万
 $22,848/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -40998,7 +40998,7 @@
           <t>B | 520呎 (2房)
 $1177万
 $22,631/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -41006,7 +41006,7 @@
           <t>C | 388呎 (1房)
 $735万
 $18,938/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -41014,7 +41014,7 @@
           <t>D | 377呎 (1房)
 $742万
 $19,682/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -41022,7 +41022,7 @@
           <t>E | 377呎 (1房)
 $728万
 $19,302/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -41030,7 +41030,7 @@
           <t>F | 525呎 (2房)
 $1136万
 $21,646/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -41045,7 +41045,7 @@
           <t>A | 757呎 (3房)
 $1712万
 $22,622/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -41053,7 +41053,7 @@
           <t>B | 520呎 (2房)
 $1194万
 $22,954/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -41061,7 +41061,7 @@
           <t>C | 388呎 (1房)
 $716万
 $18,451/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -41069,7 +41069,7 @@
           <t>D | 377呎 (1房)
 $723万
 $19,172/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -41077,7 +41077,7 @@
           <t>E | 377呎 (1房)
 $726万
 $19,265/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -41085,7 +41085,7 @@
           <t>F | 525呎 (2房)
 $1082万
 $20,615/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -41100,7 +41100,7 @@
           <t>A | 757呎 (3房)
 $1696万
 $22,398/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -41108,7 +41108,7 @@
           <t>B | 520呎 (2房)
 $1182万
 $22,725/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -41116,7 +41116,7 @@
           <t>C | 388呎 (1房)
 $714万
 $18,415/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -41124,7 +41124,7 @@
           <t>D | 377呎 (1房)
 $739万
 $19,602/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -41132,7 +41132,7 @@
           <t>E | 377呎 (1房)
 $743万
 $19,698/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -41140,7 +41140,7 @@
           <t>F | 525呎 (2房)
 $1077万
 $20,512/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -41155,7 +41155,7 @@
           <t>A | 757呎 (3房)
 $1720万
 $22,716/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -41163,7 +41163,7 @@
           <t>B | 520呎 (2房)
 $1142万
 $21,965/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -41171,7 +41171,7 @@
           <t>C | 388呎 (1房)
 $713万
 $18,376/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -41179,7 +41179,7 @@
           <t>D | 377呎 (1房)
 $720万
 $19,098/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -41187,7 +41187,7 @@
           <t>E | 377呎 (1房)
 $723万
 $19,188/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -41195,7 +41195,7 @@
           <t>F | 525呎 (2房)
 $1072万
 $20,411/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -41210,7 +41210,7 @@
           <t>A | 757呎 (3房)
 $1638万
 $21,635/呎
-(24年-05月)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -41218,7 +41218,7 @@
           <t>B | 520呎 (2房)
 $1170万
 $22,500/呎
-(24年-05月)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -41226,7 +41226,7 @@
           <t>C | 388呎 (1房)
 $713万
 $18,376/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -41234,7 +41234,7 @@
           <t>D | 377呎 (1房)
 $720万
 $19,098/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -41242,7 +41242,7 @@
           <t>E | 377呎 (1房)
 $741万
 $19,655/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -41250,7 +41250,7 @@
           <t>F | 525呎 (2房)
 $1098万
 $20,909/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -41265,7 +41265,7 @@
           <t>A | 757呎 (3房)
 $1622万
 $21,421/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -41273,7 +41273,7 @@
           <t>B | 520呎 (2房)
 $1131万
 $21,748/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -41281,7 +41281,7 @@
           <t>C | 388呎 (1房)
 $725万
 $18,693/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -41289,7 +41289,7 @@
           <t>D | 377呎 (1房)
 $732万
 $19,430/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -41297,7 +41297,7 @@
           <t>E | 378呎 (1房)
 $736万
 $19,468/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -41305,7 +41305,7 @@
           <t>F | 525呎 (2房)
 $1087万
 $20,703/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -41320,7 +41320,7 @@
           <t>A | 757呎 (3房)
 $1614万
 $21,314/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -41328,7 +41328,7 @@
           <t>B | 520呎 (2房)
 $1153万
 $22,165/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -41336,7 +41336,7 @@
           <t>C | 388呎 (1房)
 $724万
 $18,657/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -41344,7 +41344,7 @@
           <t>D | 377呎 (1房)
 $731万
 $19,390/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -41352,7 +41352,7 @@
           <t>E | 377呎 (1房)
 $717万
 $19,019/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -41360,7 +41360,7 @@
           <t>F | 525呎 (2房)
 $1081万
 $20,598/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -41375,7 +41375,7 @@
           <t>A | 757呎 (3房)
 $1645万
 $21,725/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -41383,7 +41383,7 @@
           <t>B | 520呎 (2房)
 $1120万
 $21,533/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -41391,7 +41391,7 @@
           <t>C | 388呎 (1房)
 $705万
 $18,178/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -41399,7 +41399,7 @@
           <t>D | 377呎 (1房)
 $712万
 $18,891/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -41407,7 +41407,7 @@
           <t>E | 377呎 (1房)
 $716万
 $18,981/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -41415,7 +41415,7 @@
           <t>F | 525呎 (2房)
 $1050万
 $20,008/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -41430,7 +41430,7 @@
           <t>A | 757呎 (3房)
 $1636万
 $21,618/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -41438,7 +41438,7 @@
           <t>B | 520呎 (2房)
 $1114万
 $21,425/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -41446,7 +41446,7 @@
           <t>C | 388呎 (1房)
 $721万
 $18,582/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -41454,7 +41454,7 @@
           <t>D | 377呎 (1房)
 $728万
 $19,310/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -41462,7 +41462,7 @@
           <t>E | 377呎 (1房)
 $732万
 $19,406/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -41470,7 +41470,7 @@
           <t>F | 525呎 (2房)
 $1071万
 $20,394/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -41485,7 +41485,7 @@
           <t>A | 757呎 (3房)
 $1628万
 $21,510/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -41493,7 +41493,7 @@
           <t>B | 520呎 (2房)
 $1136万
 $21,837/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -41501,7 +41501,7 @@
           <t>C | 388呎 (1房)
 $702万
 $18,103/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -41509,7 +41509,7 @@
           <t>D | 377呎 (1房)
 $709万
 $18,814/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -41517,7 +41517,7 @@
           <t>E | 377呎 (1房)
 $713万
 $18,905/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -41525,7 +41525,7 @@
           <t>F | 524呎 (2房)
 $1040万
 $19,847/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -41540,7 +41540,7 @@
           <t>A | 757呎 (3房)
 $1620万
 $21,403/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -41548,7 +41548,7 @@
           <t>B | 520呎 (2房)
 $1130万
 $21,729/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -41556,7 +41556,7 @@
           <t>C | 388呎 (1房)
 $701万
 $18,067/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -41564,7 +41564,7 @@
           <t>D | 377呎 (1房)
 $708万
 $18,777/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -41572,7 +41572,7 @@
           <t>E | 377呎 (1房)
 $729万
 $19,326/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -41580,7 +41580,7 @@
           <t>F | 525呎 (2房)
 $1060万
 $20,192/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -41595,7 +41595,7 @@
           <t>A | 757呎 (3房)
 $1612万
 $21,297/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -41603,7 +41603,7 @@
           <t>B | 520呎 (2房)
 $1124万
 $21,621/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -41611,7 +41611,7 @@
           <t>C | 388呎 (1房)
 $700万
 $18,031/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -41619,7 +41619,7 @@
           <t>D | 377呎 (1房)
 $724万
 $19,196/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -41627,7 +41627,7 @@
           <t>E | 377呎 (1房)
 $710万
 $18,830/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -41635,7 +41635,7 @@
           <t>F | 525呎 (2房)
 $1055万
 $20,091/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -41650,7 +41650,7 @@
           <t>A | 757呎 (3房)
 $1612万
 $21,297/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -41658,7 +41658,7 @@
           <t>B | 520呎 (2房)
 $1098万
 $21,106/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -41666,7 +41666,7 @@
           <t>C | 388呎 (1房)
 $734万
 $18,912/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -41674,7 +41674,7 @@
           <t>D | 377呎 (1房)
 $741万
 $19,655/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -41682,7 +41682,7 @@
           <t>E | 377呎 (1房)
 $710万
 $18,830/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -41690,7 +41690,7 @@
           <t>F | 525呎 (2房)
 $1030万
 $19,613/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -41705,7 +41705,7 @@
           <t>A | 757呎 (3房)
 $1558万
 $20,584/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -41713,7 +41713,7 @@
           <t>B | 520呎 (2房)
 $1087万
 $20,898/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -41721,7 +41721,7 @@
           <t>C | 388呎 (1房)
 $695万
 $17,907/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -41729,7 +41729,7 @@
           <t>D | 377呎 (1房)
 $719万
 $19,064/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -41737,7 +41737,7 @@
           <t>E | 377呎 (1房)
 $722万
 $19,156/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -41745,7 +41745,7 @@
           <t>F | 525呎 (2房)
 $1020万
 $19,419/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -41760,7 +41760,7 @@
           <t>A | 757呎 (3房)
 $1550万
 $20,481/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -41768,7 +41768,7 @@
           <t>B | 520呎 (2房)
 $1108万
 $21,302/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -41776,7 +41776,7 @@
           <t>C | 388呎 (1房)
 $710万
 $18,307/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -41784,7 +41784,7 @@
           <t>D | 377呎 (1房)
 $717万
 $19,027/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -41792,7 +41792,7 @@
           <t>E | 377呎 (1房)
 $721万
 $19,117/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -41800,7 +41800,7 @@
           <t>F | 525呎 (2房)
 $1039万
 $19,794/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -41815,7 +41815,7 @@
           <t>A | 757呎 (3房)
 $1543万
 $20,379/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -41823,7 +41823,7 @@
           <t>B | 520呎 (2房)
 $1102万
 $21,196/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -41831,7 +41831,7 @@
           <t>C | 388呎 (1房)
 $709万
 $18,271/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -41839,7 +41839,7 @@
           <t>D | 377呎 (1房)
 $699万
 $18,538/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -41847,7 +41847,7 @@
           <t>E | 377呎 (1房)
 $702万
 $18,626/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -41855,7 +41855,7 @@
           <t>F | 525呎 (2房)
 $1009万
 $19,227/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -41870,7 +41870,7 @@
           <t>A | 757呎 (3房)
 $1535万
 $20,277/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -41878,7 +41878,7 @@
           <t>B | 520呎 (2房)
 $1097万
 $21,088/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -41886,7 +41886,7 @@
           <t>C | 388呎 (1房)
 $691万
 $17,799/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -41894,7 +41894,7 @@
           <t>D | 377呎 (1房)
 $698万
 $18,501/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -41902,7 +41902,7 @@
           <t>E | 377呎 (1房)
 $701万
 $18,589/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -41910,7 +41910,7 @@
           <t>F | 525呎 (2房)
 $1004万
 $19,131/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -41925,7 +41925,7 @@
           <t>A | 757呎 (3房)
 $1565万
 $20,670/呎
-(24年-05月)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -41933,7 +41933,7 @@
           <t>B | 520呎 (2房)
 $1065万
 $20,485/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -41941,7 +41941,7 @@
           <t>C | 388呎 (1房)
 $706万
 $18,183/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -41949,7 +41949,7 @@
           <t>D | 377呎 (1房)
 $696万
 $18,464/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -41957,7 +41957,7 @@
           <t>E | 377呎 (1房)
 $699万
 $18,552/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -41965,7 +41965,7 @@
           <t>F | 525呎 (2房)
 $1024万
 $19,501/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -41980,7 +41980,7 @@
           <t>A | 716呎 (3房)
 $1627万
 $22,722/呎
-(24年-05月)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -41988,7 +41988,7 @@
           <t>B | 480呎 (2房)
 $1107万
 $23,058/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -41996,7 +41996,7 @@
           <t>C | 350呎 (1房)
 $736万
 $21,029/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -42004,7 +42004,7 @@
           <t>D | 340呎 (1房)
 $742万
 $21,812/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -42012,7 +42012,7 @@
           <t>E | 340呎 (1房)
 $746万
 $21,935/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -42020,7 +42020,7 @@
           <t>F | 487呎 (2房)
 $1080万
 $22,181/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
     </row>
